--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6576" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6575" uniqueCount="530">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T17:17:44+00:00</t>
+    <t>2026-03-19T09:35:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -632,515 +632,515 @@
     <t>Basic.extension:TDDUIDecision.extension:decision.extension:motivationLocale.value[x]</t>
   </si>
   <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:commentaire</t>
+  </si>
+  <si>
+    <t>commentaire</t>
+  </si>
+  <si>
+    <t>Decision.commentaire</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:commentaire.id</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:commentaire.extension</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:commentaire.url</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:commentaire.value[x]</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation</t>
+  </si>
+  <si>
+    <t>droitPrestation</t>
+  </si>
+  <si>
+    <t>DroitPrestation</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.id</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:dateOuverture</t>
+  </si>
+  <si>
+    <t>dateOuverture</t>
+  </si>
+  <si>
+    <t>DroitPrestation.dateOuverture</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:dateOuverture.id</t>
+  </si>
+  <si>
+    <t>Basic.extension.extension.extension.extension.id</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:dateOuverture.extension</t>
+  </si>
+  <si>
+    <t>Basic.extension.extension.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:dateOuverture.url</t>
+  </si>
+  <si>
+    <t>Basic.extension.extension.extension.extension.url</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:dateOuverture.value[x]</t>
+  </si>
+  <si>
+    <t>Basic.extension.extension.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:dateEcheance</t>
+  </si>
+  <si>
+    <t>dateEcheance</t>
+  </si>
+  <si>
+    <t>DroitPrestation.dateEcheance</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:dateEcheance.id</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:dateEcheance.extension</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:dateEcheance.url</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:dateEcheance.value[x]</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:existencePAG</t>
+  </si>
+  <si>
+    <t>existencePAG</t>
+  </si>
+  <si>
+    <t>DroitPrestation.existencePAG</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:existencePAG.id</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:existencePAG.extension</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:existencePAG.url</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:existencePAG.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:creton</t>
+  </si>
+  <si>
+    <t>creton</t>
+  </si>
+  <si>
+    <t>DroitPrestation.creton</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:creton.id</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:creton.extension</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:creton.url</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:creton.value[x]</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:taux</t>
+  </si>
+  <si>
+    <t>taux</t>
+  </si>
+  <si>
+    <t>DroitPrestation.taux</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:taux.id</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:taux.extension</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:taux.url</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:taux.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:commentaire</t>
+  </si>
+  <si>
+    <t>DroitPrestation.commentaire</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:commentaire.id</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:commentaire.extension</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:commentaire.url</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:commentaire.value[x]</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation</t>
+  </si>
+  <si>
+    <t>detailPrestation</t>
+  </si>
+  <si>
+    <t>DetailPrestation</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.id</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:temporaliteAccueil</t>
+  </si>
+  <si>
+    <t>temporaliteAccueil</t>
+  </si>
+  <si>
+    <t>DetailPrestation.temporaliteAccueil</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:temporaliteAccueil.id</t>
+  </si>
+  <si>
+    <t>Basic.extension.extension.extension.extension.extension.id</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:temporaliteAccueil.extension</t>
+  </si>
+  <si>
+    <t>Basic.extension.extension.extension.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:temporaliteAccueil.url</t>
+  </si>
+  <si>
+    <t>Basic.extension.extension.extension.extension.extension.url</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:temporaliteAccueil.value[x]</t>
+  </si>
+  <si>
+    <t>Basic.extension.extension.extension.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J30-TemporaliteAccueil-ROR/FHIR/JDV-J30-TemporaliteAccueil-ROR</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:accueilSequentiel</t>
+  </si>
+  <si>
+    <t>accueilSequentiel</t>
+  </si>
+  <si>
+    <t>DetailPrestation.accueilSequentiel</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:accueilSequentiel.id</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:accueilSequentiel.extension</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:accueilSequentiel.url</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:accueilSequentiel.value[x]</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:formation</t>
+  </si>
+  <si>
+    <t>formation</t>
+  </si>
+  <si>
+    <t>DetailPrestation.formation</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:formation.id</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:formation.extension</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:formation.url</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:formation.value[x]</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:montantAttribue</t>
+  </si>
+  <si>
+    <t>montantAttribue</t>
+  </si>
+  <si>
+    <t>DetailPrestation.montantAttribue</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:montantAttribue.id</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:montantAttribue.extension</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:montantAttribue.url</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:montantAttribue.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Money
+</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:frequence</t>
+  </si>
+  <si>
+    <t>frequence</t>
+  </si>
+  <si>
+    <t>DetailPrestation.frequence</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:frequence.id</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:frequence.extension</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:frequence.url</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:frequence.value[x]</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:structureAccueil</t>
+  </si>
+  <si>
+    <t>structureAccueil</t>
+  </si>
+  <si>
+    <t>DetailPrestation.StructureAccueil</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:structureAccueil.id</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:structureAccueil.extension</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:structureAccueil.url</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:structureAccueil.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-organization)
+</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge</t>
+  </si>
+  <si>
+    <t>priseCharge</t>
+  </si>
+  <si>
+    <t>PriseCharge</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.id</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:modePriseCharge</t>
+  </si>
+  <si>
+    <t>modePriseCharge</t>
+  </si>
+  <si>
+    <t>PriseCharge.modePriseCharge</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:modePriseCharge.id</t>
+  </si>
+  <si>
+    <t>Basic.extension.extension.extension.extension.extension.extension.id</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:modePriseCharge.extension</t>
+  </si>
+  <si>
+    <t>Basic.extension.extension.extension.extension.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:modePriseCharge.url</t>
+  </si>
+  <si>
+    <t>Basic.extension.extension.extension.extension.extension.extension.url</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:modePriseCharge.value[x]</t>
+  </si>
+  <si>
+    <t>Basic.extension.extension.extension.extension.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J264-ModeEtCentreDePriseEnCharge-MDPH/FHIR/JDV-J264-ModeEtCentreDePriseEnCharge-MDPH</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification</t>
+  </si>
+  <si>
+    <t>quantification</t>
+  </si>
+  <si>
+    <t>Quantification</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.id</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:valeurPriseCharge</t>
+  </si>
+  <si>
+    <t>valeurPriseCharge</t>
+  </si>
+  <si>
+    <t>Quantification.valeurPriseCharge</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:valeurPriseCharge.id</t>
+  </si>
+  <si>
+    <t>Basic.extension.extension.extension.extension.extension.extension.extension.id</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:valeurPriseCharge.extension</t>
+  </si>
+  <si>
+    <t>Basic.extension.extension.extension.extension.extension.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:valeurPriseCharge.url</t>
+  </si>
+  <si>
+    <t>Basic.extension.extension.extension.extension.extension.extension.extension.url</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:valeurPriseCharge.value[x]</t>
+  </si>
+  <si>
+    <t>Basic.extension.extension.extension.extension.extension.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integer
+</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:unitePriseCharge</t>
+  </si>
+  <si>
+    <t>unitePriseCharge</t>
+  </si>
+  <si>
+    <t>Quantification.UnitePriseCharge</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:unitePriseCharge.id</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:unitePriseCharge.extension</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:unitePriseCharge.url</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:unitePriseCharge.value[x]</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:frequencePriseCharge</t>
+  </si>
+  <si>
+    <t>frequencePriseCharge</t>
+  </si>
+  <si>
+    <t>Quantification.frequencePriseCharge</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:frequencePriseCharge.id</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:frequencePriseCharge.extension</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:frequencePriseCharge.url</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:frequencePriseCharge.value[x]</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J37-UcumUniteTemps/FHIR/JDV-J37-UcumUniteTemps</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.url</t>
+  </si>
+  <si>
+    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.value[x]</t>
+  </si>
+  <si>
     <t>base64Binary
 booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:commentaire</t>
-  </si>
-  <si>
-    <t>commentaire</t>
-  </si>
-  <si>
-    <t>Decision.commentaire</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:commentaire.id</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:commentaire.extension</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:commentaire.url</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:commentaire.value[x]</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation</t>
-  </si>
-  <si>
-    <t>droitPrestation</t>
-  </si>
-  <si>
-    <t>DroitPrestation</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.id</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:dateOuverture</t>
-  </si>
-  <si>
-    <t>dateOuverture</t>
-  </si>
-  <si>
-    <t>DroitPrestation.dateOuverture</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:dateOuverture.id</t>
-  </si>
-  <si>
-    <t>Basic.extension.extension.extension.extension.id</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:dateOuverture.extension</t>
-  </si>
-  <si>
-    <t>Basic.extension.extension.extension.extension.extension</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:dateOuverture.url</t>
-  </si>
-  <si>
-    <t>Basic.extension.extension.extension.extension.url</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:dateOuverture.value[x]</t>
-  </si>
-  <si>
-    <t>Basic.extension.extension.extension.extension.value[x]</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:dateEcheance</t>
-  </si>
-  <si>
-    <t>dateEcheance</t>
-  </si>
-  <si>
-    <t>DroitPrestation.dateEcheance</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:dateEcheance.id</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:dateEcheance.extension</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:dateEcheance.url</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:dateEcheance.value[x]</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:existencePAG</t>
-  </si>
-  <si>
-    <t>existencePAG</t>
-  </si>
-  <si>
-    <t>DroitPrestation.existencePAG</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:existencePAG.id</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:existencePAG.extension</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:existencePAG.url</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:existencePAG.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:creton</t>
-  </si>
-  <si>
-    <t>creton</t>
-  </si>
-  <si>
-    <t>DroitPrestation.creton</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:creton.id</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:creton.extension</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:creton.url</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:creton.value[x]</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:taux</t>
-  </si>
-  <si>
-    <t>taux</t>
-  </si>
-  <si>
-    <t>DroitPrestation.taux</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:taux.id</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:taux.extension</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:taux.url</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:taux.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity
-</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:commentaire</t>
-  </si>
-  <si>
-    <t>DroitPrestation.commentaire</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:commentaire.id</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:commentaire.extension</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:commentaire.url</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:commentaire.value[x]</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation</t>
-  </si>
-  <si>
-    <t>detailPrestation</t>
-  </si>
-  <si>
-    <t>DetailPrestation</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.id</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:temporaliteAccueil</t>
-  </si>
-  <si>
-    <t>temporaliteAccueil</t>
-  </si>
-  <si>
-    <t>DetailPrestation.temporaliteAccueil</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:temporaliteAccueil.id</t>
-  </si>
-  <si>
-    <t>Basic.extension.extension.extension.extension.extension.id</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:temporaliteAccueil.extension</t>
-  </si>
-  <si>
-    <t>Basic.extension.extension.extension.extension.extension.extension</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:temporaliteAccueil.url</t>
-  </si>
-  <si>
-    <t>Basic.extension.extension.extension.extension.extension.url</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:temporaliteAccueil.value[x]</t>
-  </si>
-  <si>
-    <t>Basic.extension.extension.extension.extension.extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J30-TemporaliteAccueil-ROR/FHIR/JDV-J30-TemporaliteAccueil-ROR</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:accueilSequentiel</t>
-  </si>
-  <si>
-    <t>accueilSequentiel</t>
-  </si>
-  <si>
-    <t>DetailPrestation.accueilSequentiel</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:accueilSequentiel.id</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:accueilSequentiel.extension</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:accueilSequentiel.url</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:accueilSequentiel.value[x]</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:formation</t>
-  </si>
-  <si>
-    <t>formation</t>
-  </si>
-  <si>
-    <t>DetailPrestation.formation</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:formation.id</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:formation.extension</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:formation.url</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:formation.value[x]</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:montantAttribue</t>
-  </si>
-  <si>
-    <t>montantAttribue</t>
-  </si>
-  <si>
-    <t>DetailPrestation.montantAttribue</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:montantAttribue.id</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:montantAttribue.extension</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:montantAttribue.url</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:montantAttribue.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Money
-</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:frequence</t>
-  </si>
-  <si>
-    <t>frequence</t>
-  </si>
-  <si>
-    <t>DetailPrestation.frequence</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:frequence.id</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:frequence.extension</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:frequence.url</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:frequence.value[x]</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:structureAccueil</t>
-  </si>
-  <si>
-    <t>structureAccueil</t>
-  </si>
-  <si>
-    <t>DetailPrestation.StructureAccueil</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:structureAccueil.id</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:structureAccueil.extension</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:structureAccueil.url</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:structureAccueil.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-organization)
-</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge</t>
-  </si>
-  <si>
-    <t>priseCharge</t>
-  </si>
-  <si>
-    <t>PriseCharge</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.id</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:modePriseCharge</t>
-  </si>
-  <si>
-    <t>modePriseCharge</t>
-  </si>
-  <si>
-    <t>PriseCharge.modePriseCharge</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:modePriseCharge.id</t>
-  </si>
-  <si>
-    <t>Basic.extension.extension.extension.extension.extension.extension.id</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:modePriseCharge.extension</t>
-  </si>
-  <si>
-    <t>Basic.extension.extension.extension.extension.extension.extension.extension</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:modePriseCharge.url</t>
-  </si>
-  <si>
-    <t>Basic.extension.extension.extension.extension.extension.extension.url</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:modePriseCharge.value[x]</t>
-  </si>
-  <si>
-    <t>Basic.extension.extension.extension.extension.extension.extension.value[x]</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J264-ModeEtCentreDePriseEnCharge-MDPH/FHIR/JDV-J264-ModeEtCentreDePriseEnCharge-MDPH</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification</t>
-  </si>
-  <si>
-    <t>quantification</t>
-  </si>
-  <si>
-    <t>Quantification</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.id</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:valeurPriseCharge</t>
-  </si>
-  <si>
-    <t>valeurPriseCharge</t>
-  </si>
-  <si>
-    <t>Quantification.valeurPriseCharge</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:valeurPriseCharge.id</t>
-  </si>
-  <si>
-    <t>Basic.extension.extension.extension.extension.extension.extension.extension.id</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:valeurPriseCharge.extension</t>
-  </si>
-  <si>
-    <t>Basic.extension.extension.extension.extension.extension.extension.extension.extension</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:valeurPriseCharge.url</t>
-  </si>
-  <si>
-    <t>Basic.extension.extension.extension.extension.extension.extension.extension.url</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:valeurPriseCharge.value[x]</t>
-  </si>
-  <si>
-    <t>Basic.extension.extension.extension.extension.extension.extension.extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">integer
-</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:unitePriseCharge</t>
-  </si>
-  <si>
-    <t>unitePriseCharge</t>
-  </si>
-  <si>
-    <t>Quantification.UnitePriseCharge</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:unitePriseCharge.id</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:unitePriseCharge.extension</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:unitePriseCharge.url</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:unitePriseCharge.value[x]</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:frequencePriseCharge</t>
-  </si>
-  <si>
-    <t>frequencePriseCharge</t>
-  </si>
-  <si>
-    <t>Quantification.frequencePriseCharge</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:frequencePriseCharge.id</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:frequencePriseCharge.extension</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:frequencePriseCharge.url</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:frequencePriseCharge.value[x]</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J37-UcumUniteTemps/FHIR/JDV-J37-UcumUniteTemps</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.url</t>
-  </si>
-  <si>
-    <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.value[x]</t>
   </si>
   <si>
     <t>Basic.extension:TDDUIDecision.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.url</t>
@@ -1430,7 +1430,7 @@
     <t>numeroEnregistrement</t>
   </si>
   <si>
-    <t>Numéro d'enregistrement de la décision</t>
+    <t>Numéro enregistrement de la décision</t>
   </si>
   <si>
     <t>Decision.numeroEnregistrement</t>
@@ -1452,7 +1452,7 @@
   &lt;coding&gt;
     &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-basic-decision-identifier"/&gt;
     &lt;code value="NUMENREG"/&gt;
-    &lt;display value="Numéro d'enregistrement de la décision"/&gt;
+    &lt;display value="Numéro enregistrement de la décision"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
@@ -1508,7 +1508,7 @@
     <t>Basic.identifier:idNat_Decision.system</t>
   </si>
   <si>
-    <t>1.2.250.1.213.8.1</t>
+    <t>urn:oid:1.2.250.1.213.8.1</t>
   </si>
   <si>
     <t>Basic.identifier:idNat_Decision.value</t>
@@ -1526,7 +1526,7 @@
     <t>numeroAllocataire</t>
   </si>
   <si>
-    <t>Numéro d'allocataire</t>
+    <t>Numéro allocataire</t>
   </si>
   <si>
     <t>DroitPrestation.numeroAllocataire</t>
@@ -1548,7 +1548,7 @@
   &lt;coding&gt;
     &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-basic-decision-identifier"/&gt;
     &lt;code value="NUMALLOC"/&gt;
-    &lt;display value="Numéro d'allocataire"/&gt;
+    &lt;display value="Numéro allocataire"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
@@ -4998,14 +4998,14 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>162</v>
+        <v>79</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>79</v>
@@ -5020,14 +5020,12 @@
         <v>132</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -5094,7 +5092,7 @@
         <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>151</v>
+        <v>79</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>79</v>
@@ -5239,7 +5237,7 @@
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>199</v>
+        <v>147</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>182</v>
@@ -5322,13 +5320,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>161</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>79</v>
@@ -5422,7 +5420,7 @@
         <v>138</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>79</v>
@@ -5433,7 +5431,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>170</v>
@@ -5542,7 +5540,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>172</v>
@@ -5651,7 +5649,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>174</v>
@@ -5694,7 +5692,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>79</v>
@@ -5762,7 +5760,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>180</v>
@@ -5871,13 +5869,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>161</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>79</v>
@@ -5971,7 +5969,7 @@
         <v>138</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>79</v>
@@ -5982,7 +5980,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>170</v>
@@ -6091,7 +6089,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>172</v>
@@ -6102,7 +6100,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>78</v>
@@ -6200,13 +6198,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>172</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>79</v>
@@ -6300,7 +6298,7 @@
         <v>138</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>79</v>
@@ -6311,10 +6309,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B40" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6420,10 +6418,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="B41" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6529,10 +6527,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="B42" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6572,7 +6570,7 @@
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>79</v>
@@ -6640,10 +6638,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="B43" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6749,13 +6747,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>172</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>79</v>
@@ -6849,7 +6847,7 @@
         <v>138</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>79</v>
@@ -6860,10 +6858,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6969,10 +6967,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7078,10 +7076,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7121,7 +7119,7 @@
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>79</v>
@@ -7189,10 +7187,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7298,13 +7296,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>172</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>79</v>
@@ -7398,7 +7396,7 @@
         <v>138</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>79</v>
@@ -7409,10 +7407,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7518,10 +7516,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7627,10 +7625,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7670,7 +7668,7 @@
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>79</v>
@@ -7738,10 +7736,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7764,7 +7762,7 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L53" t="s" s="2">
         <v>182</v>
@@ -7847,13 +7845,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>172</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>79</v>
@@ -7947,7 +7945,7 @@
         <v>138</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>79</v>
@@ -7958,10 +7956,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8067,10 +8065,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8176,10 +8174,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8219,7 +8217,7 @@
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="S57" t="s" s="2">
         <v>79</v>
@@ -8287,10 +8285,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8313,7 +8311,7 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L58" t="s" s="2">
         <v>182</v>
@@ -8396,13 +8394,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>172</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>79</v>
@@ -8496,7 +8494,7 @@
         <v>138</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>79</v>
@@ -8507,10 +8505,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8616,10 +8614,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8725,10 +8723,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8768,7 +8766,7 @@
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>79</v>
@@ -8836,10 +8834,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8862,7 +8860,7 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>182</v>
@@ -8945,13 +8943,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>172</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>79</v>
@@ -9045,7 +9043,7 @@
         <v>138</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>79</v>
@@ -9056,10 +9054,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9165,10 +9163,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9274,10 +9272,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9317,7 +9315,7 @@
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>79</v>
@@ -9385,10 +9383,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9494,13 +9492,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>172</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>79</v>
@@ -9594,7 +9592,7 @@
         <v>138</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>79</v>
@@ -9605,10 +9603,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9714,10 +9712,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9823,13 +9821,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="C72" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="C72" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>79</v>
@@ -9923,7 +9921,7 @@
         <v>138</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>79</v>
@@ -9934,10 +9932,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="B73" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10043,10 +10041,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="B74" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10152,10 +10150,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B75" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10195,7 +10193,7 @@
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>79</v>
@@ -10263,10 +10261,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="B76" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10289,7 +10287,7 @@
         <v>79</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L76" t="s" s="2">
         <v>182</v>
@@ -10322,11 +10320,11 @@
         <v>79</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>79</v>
@@ -10370,13 +10368,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="C77" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>79</v>
@@ -10470,7 +10468,7 @@
         <v>138</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>79</v>
@@ -10481,10 +10479,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10590,10 +10588,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10699,10 +10697,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10742,7 +10740,7 @@
       </c>
       <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="S80" t="s" s="2">
         <v>79</v>
@@ -10810,10 +10808,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10836,7 +10834,7 @@
         <v>79</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L81" t="s" s="2">
         <v>182</v>
@@ -10919,13 +10917,13 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="C82" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="C82" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="D82" t="s" s="2">
         <v>79</v>
@@ -11019,7 +11017,7 @@
         <v>138</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>79</v>
@@ -11030,10 +11028,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11139,10 +11137,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11248,10 +11246,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11291,7 +11289,7 @@
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="S85" t="s" s="2">
         <v>79</v>
@@ -11359,10 +11357,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11468,13 +11466,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="C87" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="C87" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>79</v>
@@ -11568,7 +11566,7 @@
         <v>138</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>79</v>
@@ -11579,10 +11577,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11688,10 +11686,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11797,10 +11795,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11840,7 +11838,7 @@
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>79</v>
@@ -11908,10 +11906,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11934,7 +11932,7 @@
         <v>79</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L91" t="s" s="2">
         <v>182</v>
@@ -12017,13 +12015,13 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="C92" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="C92" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="D92" t="s" s="2">
         <v>79</v>
@@ -12117,7 +12115,7 @@
         <v>138</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>79</v>
@@ -12128,10 +12126,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12237,10 +12235,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12346,10 +12344,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12389,7 +12387,7 @@
       </c>
       <c r="Q95" s="2"/>
       <c r="R95" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="S95" t="s" s="2">
         <v>79</v>
@@ -12457,10 +12455,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12483,7 +12481,7 @@
         <v>79</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L96" t="s" s="2">
         <v>182</v>
@@ -12566,13 +12564,13 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="C97" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="C97" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>79</v>
@@ -12666,7 +12664,7 @@
         <v>138</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>79</v>
@@ -12677,10 +12675,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12786,10 +12784,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12895,10 +12893,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12938,7 +12936,7 @@
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>79</v>
@@ -13006,10 +13004,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13032,7 +13030,7 @@
         <v>79</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L101" t="s" s="2">
         <v>182</v>
@@ -13115,13 +13113,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="C102" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="C102" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="D102" t="s" s="2">
         <v>79</v>
@@ -13215,7 +13213,7 @@
         <v>138</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>79</v>
@@ -13226,10 +13224,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13335,10 +13333,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13446,13 +13444,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="C105" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C105" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>79</v>
@@ -13546,7 +13544,7 @@
         <v>138</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>79</v>
@@ -13557,10 +13555,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B106" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13666,10 +13664,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="B107" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13775,10 +13773,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="B108" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13818,7 +13816,7 @@
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>79</v>
@@ -13886,10 +13884,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="B109" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13912,7 +13910,7 @@
         <v>79</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L109" t="s" s="2">
         <v>182</v>
@@ -13945,11 +13943,11 @@
         <v>79</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Y109" s="2"/>
       <c r="Z109" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>79</v>
@@ -13993,13 +13991,13 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="C110" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C110" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="D110" t="s" s="2">
         <v>79</v>
@@ -14093,7 +14091,7 @@
         <v>138</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>79</v>
@@ -14104,10 +14102,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14213,10 +14211,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14324,13 +14322,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="C113" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="C113" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>79</v>
@@ -14424,7 +14422,7 @@
         <v>138</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>79</v>
@@ -14435,10 +14433,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="B114" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14544,10 +14542,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="B115" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14653,10 +14651,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="B116" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14696,7 +14694,7 @@
       </c>
       <c r="Q116" s="2"/>
       <c r="R116" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="S116" t="s" s="2">
         <v>79</v>
@@ -14764,10 +14762,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="B117" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14790,7 +14788,7 @@
         <v>79</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="L117" t="s" s="2">
         <v>182</v>
@@ -14873,13 +14871,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="C118" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="C118" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>79</v>
@@ -14973,7 +14971,7 @@
         <v>138</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AL118" t="s" s="2">
         <v>79</v>
@@ -14984,10 +14982,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15093,10 +15091,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15202,10 +15200,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15245,7 +15243,7 @@
       </c>
       <c r="Q121" s="2"/>
       <c r="R121" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="S121" t="s" s="2">
         <v>79</v>
@@ -15313,10 +15311,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15339,7 +15337,7 @@
         <v>79</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L122" t="s" s="2">
         <v>182</v>
@@ -15422,13 +15420,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="C123" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="C123" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>79</v>
@@ -15522,7 +15520,7 @@
         <v>138</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>79</v>
@@ -15533,10 +15531,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15642,10 +15640,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15751,10 +15749,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15794,7 +15792,7 @@
       </c>
       <c r="Q126" s="2"/>
       <c r="R126" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="S126" t="s" s="2">
         <v>79</v>
@@ -15862,10 +15860,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15888,7 +15886,7 @@
         <v>79</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L127" t="s" s="2">
         <v>182</v>
@@ -15921,11 +15919,11 @@
         <v>79</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Y127" s="2"/>
       <c r="Z127" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>79</v>
@@ -15969,10 +15967,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16012,7 +16010,7 @@
       </c>
       <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="S128" t="s" s="2">
         <v>79</v>
@@ -16080,10 +16078,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16106,7 +16104,7 @@
         <v>79</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>199</v>
+        <v>366</v>
       </c>
       <c r="L129" t="s" s="2">
         <v>182</v>
@@ -16192,7 +16190,7 @@
         <v>367</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -16232,7 +16230,7 @@
       </c>
       <c r="Q130" s="2"/>
       <c r="R130" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="S130" t="s" s="2">
         <v>79</v>
@@ -16303,7 +16301,7 @@
         <v>368</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16326,7 +16324,7 @@
         <v>79</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>199</v>
+        <v>366</v>
       </c>
       <c r="L131" t="s" s="2">
         <v>182</v>
@@ -16412,7 +16410,7 @@
         <v>369</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -16452,7 +16450,7 @@
       </c>
       <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="S132" t="s" s="2">
         <v>79</v>
@@ -16523,7 +16521,7 @@
         <v>370</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -16546,7 +16544,7 @@
         <v>79</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>199</v>
+        <v>366</v>
       </c>
       <c r="L133" t="s" s="2">
         <v>182</v>
@@ -16672,7 +16670,7 @@
       </c>
       <c r="Q134" s="2"/>
       <c r="R134" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S134" t="s" s="2">
         <v>79</v>
@@ -16766,7 +16764,7 @@
         <v>79</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>199</v>
+        <v>366</v>
       </c>
       <c r="L135" t="s" s="2">
         <v>182</v>
@@ -16986,7 +16984,7 @@
         <v>79</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>199</v>
+        <v>366</v>
       </c>
       <c r="L137" t="s" s="2">
         <v>182</v>
@@ -17206,7 +17204,7 @@
         <v>79</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>199</v>
+        <v>366</v>
       </c>
       <c r="L139" t="s" s="2">
         <v>182</v>
@@ -17792,7 +17790,7 @@
         <v>79</v>
       </c>
       <c r="X144" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Y144" t="s" s="2">
         <v>401</v>
@@ -17868,7 +17866,7 @@
         <v>88</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L145" t="s" s="2">
         <v>406</v>
@@ -18793,7 +18791,7 @@
         <v>79</v>
       </c>
       <c r="X153" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Y153" t="s" s="2">
         <v>401</v>
@@ -18869,7 +18867,7 @@
         <v>88</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L154" t="s" s="2">
         <v>406</v>
@@ -18906,7 +18904,7 @@
         <v>79</v>
       </c>
       <c r="X154" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Y154" s="2"/>
       <c r="Z154" t="s" s="2">
@@ -19792,7 +19790,7 @@
         <v>79</v>
       </c>
       <c r="X162" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Y162" t="s" s="2">
         <v>401</v>
@@ -19868,7 +19866,7 @@
         <v>88</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L163" t="s" s="2">
         <v>406</v>
@@ -19905,7 +19903,7 @@
         <v>79</v>
       </c>
       <c r="X163" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Y163" s="2"/>
       <c r="Z163" t="s" s="2">
@@ -20791,7 +20789,7 @@
         <v>79</v>
       </c>
       <c r="X171" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Y171" t="s" s="2">
         <v>401</v>
@@ -20867,7 +20865,7 @@
         <v>88</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L172" t="s" s="2">
         <v>406</v>
@@ -20904,7 +20902,7 @@
         <v>79</v>
       </c>
       <c r="X172" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Y172" s="2"/>
       <c r="Z172" t="s" s="2">
@@ -21790,7 +21788,7 @@
         <v>79</v>
       </c>
       <c r="X180" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Y180" t="s" s="2">
         <v>401</v>
@@ -21866,7 +21864,7 @@
         <v>88</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L181" t="s" s="2">
         <v>406</v>
@@ -21903,7 +21901,7 @@
         <v>79</v>
       </c>
       <c r="X181" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Y181" s="2"/>
       <c r="Z181" t="s" s="2">
@@ -22421,7 +22419,7 @@
         <v>88</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L186" t="s" s="2">
         <v>500</v>
@@ -22458,7 +22456,7 @@
         <v>79</v>
       </c>
       <c r="X186" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Y186" s="2"/>
       <c r="Z186" t="s" s="2">

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T15:24:46+00:00</t>
+    <t>2026-06-09T07:55:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T07:55:39+00:00</t>
+    <t>2026-06-09T09:58:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -274,7 +274,7 @@
 7.9 Orientation vers un Service d'accompagnement familial et d'éducation précoce (SAFEP) 	Jeu(x) de valeur(s) associé(s) : JDV-J408-ORIENTATION-MS
 Seuls les codes 7 et 8 sont autorisés. {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='7.9') implies ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=7) and (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=8))}PrecisionOrientationValues8.3:Les valeurs de précision de l'orientation varient en fonction du type droit d'orientation
 8.3 Orientation en Enseignement adapté (SEGPA/EREA) 	Jeu(x) de valeur(s) associé(s) : JDV-J408-ORIENTATION-MS
-Seuls les codes 9 et 10 sont autorisés. {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.3') implies ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=9) and (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=10))}cretonCardinality:Obligatoire pour les décisions orientations ESSMS enfant, non prévu pour les autres orientations. {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='7') implies (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='creton').exists())}DateEffetClotureCardinality:Cet attribut est obligatoire pour les décisions de type 5 (Clôture de droit).  {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.where(url='decision').extension.where(url='typeDecision').valueCodeableConcept.coding.code='5') implies ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.where(url='decision').extension.where(url='dateEffetCloture').exists()))}temporaliteAccueilCardinalityViaTypeDroitPrestation:La temporalité d'accueil est transmise pour les types de droit et prestation suivants :
+Seuls les codes 9 et 10 sont autorisés. {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.3') implies ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=9) and (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=10))}cretonCardinality:Obligatoire pour les décisions orientations ESSMS enfant {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='7') implies (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='creton').exists())}DateEffetClotureCardinality:Cet attribut est obligatoire pour les décisions de type 5 (Clôture de droit).  {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.where(url='decision').extension.where(url='typeDecision').valueCodeableConcept.coding.code='5') implies ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.where(url='decision').extension.where(url='dateEffetCloture').exists()))}temporaliteAccueilCardinalityViaTypeDroitPrestation:La temporalité d'accueil est transmise pour les types de droit et prestation suivants :
     Orientation en Unité d'enseignement
     Orientation vers une Scolarisation en milieu ordinaire à temps partagé (UE et établissement scolaire)
     Orientation vers une Unité d'enseignement et une scolarisation en ULIS à temps partagé

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T09:58:53+00:00</t>
+    <t>2026-06-10T14:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -274,7 +274,7 @@
 7.9 Orientation vers un Service d'accompagnement familial et d'éducation précoce (SAFEP) 	Jeu(x) de valeur(s) associé(s) : JDV-J408-ORIENTATION-MS
 Seuls les codes 7 et 8 sont autorisés. {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='7.9') implies ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=7) and (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=8))}PrecisionOrientationValues8.3:Les valeurs de précision de l'orientation varient en fonction du type droit d'orientation
 8.3 Orientation en Enseignement adapté (SEGPA/EREA) 	Jeu(x) de valeur(s) associé(s) : JDV-J408-ORIENTATION-MS
-Seuls les codes 9 et 10 sont autorisés. {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.3') implies ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=9) and (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=10))}cretonCardinality:Obligatoire pour les décisions orientations ESSMS enfant {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='7') implies (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='creton').exists())}DateEffetClotureCardinality:Cet attribut est obligatoire pour les décisions de type 5 (Clôture de droit).  {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.where(url='decision').extension.where(url='typeDecision').valueCodeableConcept.coding.code='5') implies ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.where(url='decision').extension.where(url='dateEffetCloture').exists()))}temporaliteAccueilCardinalityViaTypeDroitPrestation:La temporalité d'accueil est transmise pour les types de droit et prestation suivants :
+Seuls les codes 9 et 10 sont autorisés. {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.3') implies ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=9) and (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=10))}cretonCardinality:Obligatoire pour les décisions orientations ESSMS enfant {((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='7') or (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code.matches('^7[.][0-9]+$'))) implies (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='creton').exists())}DateEffetClotureCardinality:Cet attribut est obligatoire pour les décisions de type 5 (Clôture de droit).  {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.where(url='decision').extension.where(url='typeDecision').valueCodeableConcept.coding.code='5') implies ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.where(url='decision').extension.where(url='dateEffetCloture').exists()))}temporaliteAccueilCardinalityViaTypeDroitPrestation:La temporalité d'accueil est transmise pour les types de droit et prestation suivants :
     Orientation en Unité d'enseignement
     Orientation vers une Scolarisation en milieu ordinaire à temps partagé (UE et établissement scolaire)
     Orientation vers une Unité d'enseignement et une scolarisation en ULIS à temps partagé

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T14:13:27+00:00</t>
+    <t>2026-06-12T15:13:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T13:25:13+00:00</t>
+    <t>2026-06-16T07:36:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T07:36:31+00:00</t>
+    <t>2026-06-16T07:55:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T07:55:16+00:00</t>
+    <t>2026-06-16T08:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T08:15:37+00:00</t>
+    <t>2026-06-17T09:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T09:17:48+00:00</t>
+    <t>2026-06-17T09:36:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T09:36:47+00:00</t>
+    <t>2026-06-19T10:27:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -267,23 +267,8 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}motivationLocaleRequired:La motivation locale doit être renseignée si la motivation de la décision est '9999 - Autre' (code de la nomenclature de référence jdv-j399-motivation-ms). {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='motivation').valueCodeableConcept.coding.code='215')
- implies ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='motivationLocale').valueString.exists()))}idDecisionMAJCardinality:l'idDecisionMAJ est obligatoire si typeDecision = '5' (Clôture de droit) ou typeDecision ='1' (Attribution) et DroitPrestation.natureDroit = '6' (Renouvellement) ou '7' (Révision). {((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='typeDecision').valueCodeableConcept.coding.code='1') and ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='natureDroitPrestation').valueCodeableConcept=6) or (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='natureDroitPrestation').valueCodeableConcept=7))) implies (identifier.where(type.coding.code='IDDECISIONMAJ').exists())}idDecisionMAJInterdiction:l'idDecisionMAJ n'est pas à transmettre si typeDecision = '1' (Attribution) et DroitPrestation.natureDroit = '1' (Nouveau droit) {((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='typeDecision').valueCodeableConcept.coding.code='1') and (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='natureDroitPrestation').valueCodeableConcept=1)) implies (identifier.where(type.coding.code='IDDECISIONMAJ').exists().not())}FormationCardinality:Formation est obligatoire si le type de droit et prestation est 11.1 (Orientation en Centre de rééducation professionnelle (CRP)). {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='11.1') implies (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='formation').exists())}PrecisionOrientationValues7.8:Les valeurs de précision de l'orientation varient en fonction du type droit d'orientation
-7.8 Orientation vers un Service d'éducation spéciale et de soins à domicile (SESSAD) 	Jeu(x) de valeur(s) associé(s) : JDV-J408-ORIENTATION-MS
-Seuls les codes de 1 à 6 sont autorisés. {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='7.8') implies ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=1) and (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=6))}PrecisionOrientationValues7.9:Les valeurs de précision de l'orientation varient en fonction du type droit d'orientation
-7.9 Orientation vers un Service d'accompagnement familial et d'éducation précoce (SAFEP) 	Jeu(x) de valeur(s) associé(s) : JDV-J408-ORIENTATION-MS
-Seuls les codes 7 et 8 sont autorisés. {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='7.9') implies ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=7) and (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=8))}PrecisionOrientationValues8.3:Les valeurs de précision de l'orientation varient en fonction du type droit d'orientation
-8.3 Orientation en Enseignement adapté (SEGPA/EREA) 	Jeu(x) de valeur(s) associé(s) : JDV-J408-ORIENTATION-MS
-Seuls les codes 9 et 10 sont autorisés. {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.3') implies ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=9) and (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=10))}cretonCardinality:Obligatoire pour les décisions orientations ESSMS enfant {((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='7') or (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code.matches('^7[.][0-9]+$'))) implies (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='creton').exists())}DateEffetClotureCardinality:Cet attribut est obligatoire pour les décisions de type 5 (Clôture de droit).  {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.where(url='decision').extension.where(url='typeDecision').valueCodeableConcept.coding.code='5') implies ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.where(url='decision').extension.where(url='dateEffetCloture').exists()))}temporaliteAccueilCardinalityViaTypeDroitPrestation:La temporalité d'accueil est transmise pour les types de droit et prestation suivants :
-    Orientation en Unité d'enseignement
-    Orientation vers une Scolarisation en milieu ordinaire à temps partagé (UE et établissement scolaire)
-    Orientation vers une Unité d'enseignement et une scolarisation en ULIS à temps partagé
-    Orientation vers une unité d'enseignement et une scolarisation en enseignement adapté à temps partagé
- {((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.6') or (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.7') or (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.8') or (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.10')) implies (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil').exists())}temporaliteAccueilCardinalityViaCategorieDroitPrestation:La temporalité d'accueil est transmise pour tous les droits pour lesquels elle est obligatoire.
-Pour les catégories de droit et prestation suivantes :
-    Orientation ESMS Enfants
-    Orientation ESMS Adultes
- {((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='13') or (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='7')) implies (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil').exists())}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}motivationLocaleRequired:La motivation locale doit être renseignée si la motivation de la décision est '9999' (Autre). {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='motivation').valueCodeableConcept.coding.code='215')
+ implies ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='motivationLocale').valueString.exists()))}idDecisionMAJCardinality:l'idDecisionMAJ est obligatoire si typeDecision = '5' (Clôture de droit) ou typeDecision ='1' (Attribution) et DroitPrestation.natureDroit = '6' (Renouvellement) ou '7' (Révision). {((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='typeDecision').valueCodeableConcept.coding.code='1') and ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='natureDroitPrestation').valueCodeableConcept=6) or (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='natureDroitPrestation').valueCodeableConcept=7))) implies (identifier.where(type.coding.code='IDDECISIONMAJ').exists())}idDecisionMAJInterdiction:l'idDecisionMAJ n'est pas à transmettre si typeDecision = '1' (Attribution) et DroitPrestation.natureDroit = '1' (Attribution) {((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='typeDecision').valueCodeableConcept.coding.code='1') and (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='natureDroitPrestation').valueCodeableConcept=1)) implies (identifier.where(type.coding.code='IDDECISIONMAJ').exists().not())}FormationCardinality:Formation est obligatoire si le type de droit et prestation est '11.1' (Orientation en Centre de rééducation professionnelle (CRP)). {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='11.1') implies (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='formation').exists())}PrecisionOrientationValues7.8:Si typeDroitPrestation = '7.8' (Orientation vers un Service d'éducation spéciale et de soins à domicile (SESSAD)) alors precisionOrientation = '1' (SESSAD polyvalent) ou '6' (SESSAD pour troubles du langage et des apprentissages). {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='7.8') implies ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=1) and (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=6))}PrecisionOrientationValues7.9:Si typeDroitPrestation = '7.9' (Orientation vers un Service d'accompagnement familial et d'éducation précoce (SAFEP)) alors precisionOrientation = '7' (SAFEP déficience auditive) ou '8' (SAFEP déficience visuelle). {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='7.9') implies ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=7) and (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=8))}PrecisionOrientationValues8.3:Si typeDroitPrestation = '8.3' (Orientation en Enseignement adapté (SEGPA/EREA)) alors precisionOrientation = '9' (Scolarisation en SEGPA (sections d’enseignement général et professionnel adapté)) ou '10' (Scolarisation en EREA (établissements régionaux d’enseignement adapté)). {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.3') implies ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=9) and (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=10))}PrecisionOrientationValues8.6:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) alors precisionOrientation = 'UEA' (Unité d'enseignement élémentaire autisme) ou 'UEM' (Unité d'enseignement en maternelle plan autisme). {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.6') implies ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code='UEA') or (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code='UEM'))}cretonCardinality:Si categorieDroitPrestation = '7' (ESSMS enfant) alors Creton est obligatoire {((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='7') or (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code.matches('^7[.][0-9]+$'))) implies (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='creton').exists())}DateEffetClotureCardinality:Si typeDecision = '5' (Clôture de droit) alors dateEffetCloture est obligatoire. {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.where(url='decision').extension.where(url='typeDecision').valueCodeableConcept.coding.code='5') implies ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.where(url='decision').extension.where(url='dateEffetCloture').exists()))}temporaliteAccueilCardinalityViaTypeDroitPrestation:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) ou '8.7' (Orientation vers une Scolarisation en milieu ordinaire à temps partagé) ou '8.8' (Orientation vers une Unité d'enseignement et une scolarisation en ULIS à temps partagé) ou '8.10' (Orientation vers une unité d'enseignement et une scolarisation en enseignement adapté à temps partagé) alors la temporalité d'accueil est obligatoire. {((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.6') or (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.7') or (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.8') or (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.10')) implies (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil').exists())}temporaliteAccueilCardinalityViaCategorieDroitPrestation:Si categorieDroitPrestation = '13' (Orientation ESMS Enfants) ou '7' (Orientation ESMS Adultes) alors la temporalité d'accueil est obligatoire. {((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='13') or (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='7')) implies (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil').exists())}PrecisionOrientationValues13.1-13.2:Si typeDroitPrestation = '13.1' (Orientation vers un établissement d'accueil non médicalisé) ou '13.2' (Orientation vers un établissement d'accueil médicalisé en tout ou partie) alors precisionOrientation est interdit {((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='13.1') or (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='13.2')) implies (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').exists().not())}</t>
   </si>
   <si>
     <t>Decision</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8428" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8427" uniqueCount="612">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T10:27:30+00:00</t>
+    <t>2026-06-22T09:32:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1492,13 +1492,7 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-basic-decision-identifier</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1621,9 +1615,6 @@
     &lt;display value="Identifiant principal de la décision"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-basic-decision-identifier</t>
   </si>
   <si>
     <t>Basic.identifier:idDecision.system</t>
@@ -2258,7 +2249,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="40.33203125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="106.02734375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -23086,31 +23077,29 @@
         <v>79</v>
       </c>
       <c r="X190" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="Y190" s="2"/>
+      <c r="Z190" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="Y190" t="s" s="2">
+      <c r="AA190" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB190" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC190" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD190" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE190" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF190" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="Z190" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AA190" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB190" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC190" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD190" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE190" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF190" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>77</v>
@@ -23136,10 +23125,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -23165,16 +23154,16 @@
         <v>101</v>
       </c>
       <c r="L191" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M191" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N191" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M191" t="s" s="2">
+      <c r="O191" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="N191" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="O191" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>79</v>
@@ -23187,7 +23176,7 @@
         <v>79</v>
       </c>
       <c r="T191" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="U191" t="s" s="2">
         <v>79</v>
@@ -23223,7 +23212,7 @@
         <v>79</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>77</v>
@@ -23241,7 +23230,7 @@
         <v>79</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="AM191" t="s" s="2">
         <v>79</v>
@@ -23249,10 +23238,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -23278,13 +23267,13 @@
         <v>147</v>
       </c>
       <c r="L192" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M192" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="N192" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M192" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N192" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="O192" s="2"/>
       <c r="P192" t="s" s="2">
@@ -23298,7 +23287,7 @@
         <v>79</v>
       </c>
       <c r="T192" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="U192" t="s" s="2">
         <v>79</v>
@@ -23334,7 +23323,7 @@
         <v>79</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>77</v>
@@ -23352,7 +23341,7 @@
         <v>79</v>
       </c>
       <c r="AL192" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AM192" t="s" s="2">
         <v>79</v>
@@ -23360,10 +23349,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -23386,13 +23375,13 @@
         <v>88</v>
       </c>
       <c r="K193" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="L193" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M193" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="L193" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="M193" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="N193" s="2"/>
       <c r="O193" s="2"/>
@@ -23443,7 +23432,7 @@
         <v>79</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>77</v>
@@ -23461,7 +23450,7 @@
         <v>79</v>
       </c>
       <c r="AL193" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AM193" t="s" s="2">
         <v>79</v>
@@ -23469,10 +23458,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -23495,16 +23484,16 @@
         <v>88</v>
       </c>
       <c r="K194" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="L194" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M194" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="L194" t="s" s="2">
+      <c r="N194" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="M194" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N194" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
@@ -23554,7 +23543,7 @@
         <v>79</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>77</v>
@@ -23572,7 +23561,7 @@
         <v>79</v>
       </c>
       <c r="AL194" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AM194" t="s" s="2">
         <v>79</v>
@@ -23580,13 +23569,13 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B195" t="s" s="2">
         <v>459</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D195" t="s" s="2">
         <v>79</v>
@@ -23611,7 +23600,7 @@
         <v>460</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="M195" t="s" s="2">
         <v>462</v>
@@ -23680,7 +23669,7 @@
         <v>99</v>
       </c>
       <c r="AK195" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="AL195" t="s" s="2">
         <v>464</v>
@@ -23691,7 +23680,7 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B196" t="s" s="2">
         <v>466</v>
@@ -23800,7 +23789,7 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B197" t="s" s="2">
         <v>467</v>
@@ -23911,7 +23900,7 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>468</v>
@@ -24024,7 +24013,7 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B199" t="s" s="2">
         <v>477</v>
@@ -24072,7 +24061,7 @@
         <v>79</v>
       </c>
       <c r="S199" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="T199" t="s" s="2">
         <v>79</v>
@@ -24091,7 +24080,7 @@
       </c>
       <c r="Y199" s="2"/>
       <c r="Z199" t="s" s="2">
-        <v>523</v>
+        <v>482</v>
       </c>
       <c r="AA199" t="s" s="2">
         <v>79</v>
@@ -24109,7 +24098,7 @@
         <v>79</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>77</v>
@@ -24135,10 +24124,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -24164,16 +24153,16 @@
         <v>101</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="M200" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N200" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="O200" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="N200" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="O200" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>79</v>
@@ -24186,7 +24175,7 @@
         <v>79</v>
       </c>
       <c r="T200" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="U200" t="s" s="2">
         <v>79</v>
@@ -24222,7 +24211,7 @@
         <v>79</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>77</v>
@@ -24240,7 +24229,7 @@
         <v>79</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="AM200" t="s" s="2">
         <v>79</v>
@@ -24248,10 +24237,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -24277,13 +24266,13 @@
         <v>147</v>
       </c>
       <c r="L201" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M201" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="N201" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M201" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N201" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
@@ -24297,7 +24286,7 @@
         <v>79</v>
       </c>
       <c r="T201" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="U201" t="s" s="2">
         <v>79</v>
@@ -24333,7 +24322,7 @@
         <v>79</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>77</v>
@@ -24351,7 +24340,7 @@
         <v>79</v>
       </c>
       <c r="AL201" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AM201" t="s" s="2">
         <v>79</v>
@@ -24359,10 +24348,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -24385,13 +24374,13 @@
         <v>88</v>
       </c>
       <c r="K202" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="L202" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M202" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="L202" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="M202" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
@@ -24442,7 +24431,7 @@
         <v>79</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>77</v>
@@ -24460,7 +24449,7 @@
         <v>79</v>
       </c>
       <c r="AL202" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AM202" t="s" s="2">
         <v>79</v>
@@ -24468,10 +24457,10 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -24494,16 +24483,16 @@
         <v>88</v>
       </c>
       <c r="K203" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="L203" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M203" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="L203" t="s" s="2">
+      <c r="N203" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="M203" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N203" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="O203" s="2"/>
       <c r="P203" t="s" s="2">
@@ -24553,7 +24542,7 @@
         <v>79</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>77</v>
@@ -24571,7 +24560,7 @@
         <v>79</v>
       </c>
       <c r="AL203" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AM203" t="s" s="2">
         <v>79</v>
@@ -24579,13 +24568,13 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B204" t="s" s="2">
         <v>459</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D204" t="s" s="2">
         <v>79</v>
@@ -24610,7 +24599,7 @@
         <v>460</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="M204" t="s" s="2">
         <v>462</v>
@@ -24679,7 +24668,7 @@
         <v>99</v>
       </c>
       <c r="AK204" t="s" s="2">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="AL204" t="s" s="2">
         <v>464</v>
@@ -24690,7 +24679,7 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B205" t="s" s="2">
         <v>466</v>
@@ -24799,7 +24788,7 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="B206" t="s" s="2">
         <v>467</v>
@@ -24910,7 +24899,7 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B207" t="s" s="2">
         <v>468</v>
@@ -25023,7 +25012,7 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B208" t="s" s="2">
         <v>477</v>
@@ -25071,7 +25060,7 @@
         <v>79</v>
       </c>
       <c r="S208" t="s" s="2">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="T208" t="s" s="2">
         <v>79</v>
@@ -25090,7 +25079,7 @@
       </c>
       <c r="Y208" s="2"/>
       <c r="Z208" t="s" s="2">
-        <v>523</v>
+        <v>482</v>
       </c>
       <c r="AA208" t="s" s="2">
         <v>79</v>
@@ -25108,7 +25097,7 @@
         <v>79</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>77</v>
@@ -25134,10 +25123,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -25163,16 +25152,16 @@
         <v>101</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="M209" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N209" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="O209" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="N209" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="O209" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="P209" t="s" s="2">
         <v>79</v>
@@ -25185,7 +25174,7 @@
         <v>79</v>
       </c>
       <c r="T209" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="U209" t="s" s="2">
         <v>79</v>
@@ -25221,7 +25210,7 @@
         <v>79</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>77</v>
@@ -25239,7 +25228,7 @@
         <v>79</v>
       </c>
       <c r="AL209" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="AM209" t="s" s="2">
         <v>79</v>
@@ -25247,10 +25236,10 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -25276,13 +25265,13 @@
         <v>147</v>
       </c>
       <c r="L210" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M210" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="N210" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M210" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N210" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
@@ -25296,7 +25285,7 @@
         <v>79</v>
       </c>
       <c r="T210" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="U210" t="s" s="2">
         <v>79</v>
@@ -25332,7 +25321,7 @@
         <v>79</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>77</v>
@@ -25350,7 +25339,7 @@
         <v>79</v>
       </c>
       <c r="AL210" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AM210" t="s" s="2">
         <v>79</v>
@@ -25358,10 +25347,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -25384,13 +25373,13 @@
         <v>88</v>
       </c>
       <c r="K211" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="L211" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M211" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="L211" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="M211" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="N211" s="2"/>
       <c r="O211" s="2"/>
@@ -25441,7 +25430,7 @@
         <v>79</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>77</v>
@@ -25459,7 +25448,7 @@
         <v>79</v>
       </c>
       <c r="AL211" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AM211" t="s" s="2">
         <v>79</v>
@@ -25467,10 +25456,10 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -25493,16 +25482,16 @@
         <v>88</v>
       </c>
       <c r="K212" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="L212" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M212" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="L212" t="s" s="2">
+      <c r="N212" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="M212" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N212" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
@@ -25552,7 +25541,7 @@
         <v>79</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>77</v>
@@ -25570,7 +25559,7 @@
         <v>79</v>
       </c>
       <c r="AL212" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AM212" t="s" s="2">
         <v>79</v>
@@ -25578,13 +25567,13 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B213" t="s" s="2">
         <v>459</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D213" t="s" s="2">
         <v>79</v>
@@ -25609,7 +25598,7 @@
         <v>460</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="M213" t="s" s="2">
         <v>462</v>
@@ -25678,7 +25667,7 @@
         <v>99</v>
       </c>
       <c r="AK213" t="s" s="2">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="AL213" t="s" s="2">
         <v>464</v>
@@ -25689,7 +25678,7 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B214" t="s" s="2">
         <v>466</v>
@@ -25798,7 +25787,7 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="B215" t="s" s="2">
         <v>467</v>
@@ -25909,7 +25898,7 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B216" t="s" s="2">
         <v>468</v>
@@ -26022,7 +26011,7 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B217" t="s" s="2">
         <v>477</v>
@@ -26070,7 +26059,7 @@
         <v>79</v>
       </c>
       <c r="S217" t="s" s="2">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="T217" t="s" s="2">
         <v>79</v>
@@ -26089,7 +26078,7 @@
       </c>
       <c r="Y217" s="2"/>
       <c r="Z217" t="s" s="2">
-        <v>523</v>
+        <v>482</v>
       </c>
       <c r="AA217" t="s" s="2">
         <v>79</v>
@@ -26107,7 +26096,7 @@
         <v>79</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>77</v>
@@ -26133,10 +26122,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -26162,16 +26151,16 @@
         <v>101</v>
       </c>
       <c r="L218" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M218" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N218" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M218" t="s" s="2">
+      <c r="O218" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="N218" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="O218" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="P218" t="s" s="2">
         <v>79</v>
@@ -26181,10 +26170,10 @@
         <v>79</v>
       </c>
       <c r="S218" t="s" s="2">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="T218" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="U218" t="s" s="2">
         <v>79</v>
@@ -26220,7 +26209,7 @@
         <v>79</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>77</v>
@@ -26238,7 +26227,7 @@
         <v>79</v>
       </c>
       <c r="AL218" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="AM218" t="s" s="2">
         <v>79</v>
@@ -26246,10 +26235,10 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -26275,13 +26264,13 @@
         <v>147</v>
       </c>
       <c r="L219" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M219" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="N219" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M219" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N219" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="O219" s="2"/>
       <c r="P219" t="s" s="2">
@@ -26295,7 +26284,7 @@
         <v>79</v>
       </c>
       <c r="T219" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="U219" t="s" s="2">
         <v>79</v>
@@ -26331,7 +26320,7 @@
         <v>79</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>77</v>
@@ -26349,7 +26338,7 @@
         <v>79</v>
       </c>
       <c r="AL219" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AM219" t="s" s="2">
         <v>79</v>
@@ -26357,10 +26346,10 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -26383,13 +26372,13 @@
         <v>88</v>
       </c>
       <c r="K220" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="L220" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M220" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="L220" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="M220" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="N220" s="2"/>
       <c r="O220" s="2"/>
@@ -26440,7 +26429,7 @@
         <v>79</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>77</v>
@@ -26458,7 +26447,7 @@
         <v>79</v>
       </c>
       <c r="AL220" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AM220" t="s" s="2">
         <v>79</v>
@@ -26466,10 +26455,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -26492,16 +26481,16 @@
         <v>88</v>
       </c>
       <c r="K221" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="L221" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M221" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="L221" t="s" s="2">
+      <c r="N221" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="M221" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N221" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="O221" s="2"/>
       <c r="P221" t="s" s="2">
@@ -26551,7 +26540,7 @@
         <v>79</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>77</v>
@@ -26569,7 +26558,7 @@
         <v>79</v>
       </c>
       <c r="AL221" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AM221" t="s" s="2">
         <v>79</v>
@@ -26577,13 +26566,13 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B222" t="s" s="2">
         <v>459</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="D222" t="s" s="2">
         <v>79</v>
@@ -26608,7 +26597,7 @@
         <v>460</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="M222" t="s" s="2">
         <v>462</v>
@@ -26677,7 +26666,7 @@
         <v>99</v>
       </c>
       <c r="AK222" t="s" s="2">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="AL222" t="s" s="2">
         <v>464</v>
@@ -26688,7 +26677,7 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B223" t="s" s="2">
         <v>466</v>
@@ -26797,7 +26786,7 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B224" t="s" s="2">
         <v>467</v>
@@ -26908,7 +26897,7 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B225" t="s" s="2">
         <v>468</v>
@@ -27021,7 +27010,7 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B226" t="s" s="2">
         <v>477</v>
@@ -27069,7 +27058,7 @@
         <v>79</v>
       </c>
       <c r="S226" t="s" s="2">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="T226" t="s" s="2">
         <v>79</v>
@@ -27088,7 +27077,7 @@
       </c>
       <c r="Y226" s="2"/>
       <c r="Z226" t="s" s="2">
-        <v>523</v>
+        <v>482</v>
       </c>
       <c r="AA226" t="s" s="2">
         <v>79</v>
@@ -27106,7 +27095,7 @@
         <v>79</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>77</v>
@@ -27132,10 +27121,10 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -27161,16 +27150,16 @@
         <v>101</v>
       </c>
       <c r="L227" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M227" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N227" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M227" t="s" s="2">
+      <c r="O227" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="N227" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="O227" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="P227" t="s" s="2">
         <v>79</v>
@@ -27180,10 +27169,10 @@
         <v>79</v>
       </c>
       <c r="S227" t="s" s="2">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="T227" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="U227" t="s" s="2">
         <v>79</v>
@@ -27219,7 +27208,7 @@
         <v>79</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>77</v>
@@ -27237,7 +27226,7 @@
         <v>79</v>
       </c>
       <c r="AL227" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="AM227" t="s" s="2">
         <v>79</v>
@@ -27245,10 +27234,10 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -27274,13 +27263,13 @@
         <v>147</v>
       </c>
       <c r="L228" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M228" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="N228" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M228" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N228" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="O228" s="2"/>
       <c r="P228" t="s" s="2">
@@ -27294,7 +27283,7 @@
         <v>79</v>
       </c>
       <c r="T228" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="U228" t="s" s="2">
         <v>79</v>
@@ -27330,7 +27319,7 @@
         <v>79</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>77</v>
@@ -27348,7 +27337,7 @@
         <v>79</v>
       </c>
       <c r="AL228" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AM228" t="s" s="2">
         <v>79</v>
@@ -27356,10 +27345,10 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -27382,13 +27371,13 @@
         <v>88</v>
       </c>
       <c r="K229" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="L229" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M229" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="L229" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="M229" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -27439,7 +27428,7 @@
         <v>79</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>77</v>
@@ -27457,7 +27446,7 @@
         <v>79</v>
       </c>
       <c r="AL229" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AM229" t="s" s="2">
         <v>79</v>
@@ -27465,10 +27454,10 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -27491,16 +27480,16 @@
         <v>88</v>
       </c>
       <c r="K230" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="L230" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M230" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="L230" t="s" s="2">
+      <c r="N230" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="M230" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N230" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="O230" s="2"/>
       <c r="P230" t="s" s="2">
@@ -27550,7 +27539,7 @@
         <v>79</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>77</v>
@@ -27568,7 +27557,7 @@
         <v>79</v>
       </c>
       <c r="AL230" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AM230" t="s" s="2">
         <v>79</v>
@@ -27576,13 +27565,13 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B231" t="s" s="2">
         <v>459</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="D231" t="s" s="2">
         <v>79</v>
@@ -27607,7 +27596,7 @@
         <v>460</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="M231" t="s" s="2">
         <v>462</v>
@@ -27676,7 +27665,7 @@
         <v>99</v>
       </c>
       <c r="AK231" t="s" s="2">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="AL231" t="s" s="2">
         <v>464</v>
@@ -27687,7 +27676,7 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B232" t="s" s="2">
         <v>466</v>
@@ -27796,7 +27785,7 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B233" t="s" s="2">
         <v>467</v>
@@ -27907,7 +27896,7 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B234" t="s" s="2">
         <v>468</v>
@@ -28020,7 +28009,7 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B235" t="s" s="2">
         <v>477</v>
@@ -28068,7 +28057,7 @@
         <v>79</v>
       </c>
       <c r="S235" t="s" s="2">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="T235" t="s" s="2">
         <v>79</v>
@@ -28087,7 +28076,7 @@
       </c>
       <c r="Y235" s="2"/>
       <c r="Z235" t="s" s="2">
-        <v>523</v>
+        <v>482</v>
       </c>
       <c r="AA235" t="s" s="2">
         <v>79</v>
@@ -28105,7 +28094,7 @@
         <v>79</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>77</v>
@@ -28131,10 +28120,10 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -28160,16 +28149,16 @@
         <v>101</v>
       </c>
       <c r="L236" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M236" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N236" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M236" t="s" s="2">
+      <c r="O236" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="N236" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="O236" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="P236" t="s" s="2">
         <v>79</v>
@@ -28179,10 +28168,10 @@
         <v>79</v>
       </c>
       <c r="S236" t="s" s="2">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="T236" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="U236" t="s" s="2">
         <v>79</v>
@@ -28218,7 +28207,7 @@
         <v>79</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>77</v>
@@ -28236,7 +28225,7 @@
         <v>79</v>
       </c>
       <c r="AL236" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="AM236" t="s" s="2">
         <v>79</v>
@@ -28244,10 +28233,10 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -28273,13 +28262,13 @@
         <v>147</v>
       </c>
       <c r="L237" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M237" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="N237" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M237" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N237" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="O237" s="2"/>
       <c r="P237" t="s" s="2">
@@ -28293,7 +28282,7 @@
         <v>79</v>
       </c>
       <c r="T237" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="U237" t="s" s="2">
         <v>79</v>
@@ -28329,7 +28318,7 @@
         <v>79</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>77</v>
@@ -28347,7 +28336,7 @@
         <v>79</v>
       </c>
       <c r="AL237" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AM237" t="s" s="2">
         <v>79</v>
@@ -28355,10 +28344,10 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -28381,13 +28370,13 @@
         <v>88</v>
       </c>
       <c r="K238" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="L238" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M238" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="L238" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="M238" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="N238" s="2"/>
       <c r="O238" s="2"/>
@@ -28438,7 +28427,7 @@
         <v>79</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>77</v>
@@ -28456,7 +28445,7 @@
         <v>79</v>
       </c>
       <c r="AL238" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AM238" t="s" s="2">
         <v>79</v>
@@ -28464,10 +28453,10 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -28490,16 +28479,16 @@
         <v>88</v>
       </c>
       <c r="K239" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="L239" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M239" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="L239" t="s" s="2">
+      <c r="N239" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="M239" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N239" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="O239" s="2"/>
       <c r="P239" t="s" s="2">
@@ -28549,7 +28538,7 @@
         <v>79</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>77</v>
@@ -28567,7 +28556,7 @@
         <v>79</v>
       </c>
       <c r="AL239" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AM239" t="s" s="2">
         <v>79</v>
@@ -28575,10 +28564,10 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -28604,16 +28593,16 @@
         <v>177</v>
       </c>
       <c r="L240" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="M240" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="N240" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="O240" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="M240" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="N240" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="O240" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="P240" t="s" s="2">
         <v>79</v>
@@ -28623,7 +28612,7 @@
         <v>79</v>
       </c>
       <c r="S240" t="s" s="2">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="T240" t="s" s="2">
         <v>79</v>
@@ -28642,7 +28631,7 @@
       </c>
       <c r="Y240" s="2"/>
       <c r="Z240" t="s" s="2">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="AA240" t="s" s="2">
         <v>79</v>
@@ -28660,7 +28649,7 @@
         <v>79</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>87</v>
@@ -28678,18 +28667,18 @@
         <v>79</v>
       </c>
       <c r="AL240" t="s" s="2">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="AM240" t="s" s="2">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -28712,19 +28701,19 @@
         <v>88</v>
       </c>
       <c r="K241" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="L241" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="M241" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="N241" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="L241" t="s" s="2">
+      <c r="O241" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="M241" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="N241" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="O241" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="P241" t="s" s="2">
         <v>79</v>
@@ -28773,7 +28762,7 @@
         <v>79</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>77</v>
@@ -28788,21 +28777,21 @@
         <v>99</v>
       </c>
       <c r="AK241" t="s" s="2">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="AL241" t="s" s="2">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="AM241" t="s" s="2">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -28828,14 +28817,14 @@
         <v>190</v>
       </c>
       <c r="L242" t="s" s="2">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="N242" s="2"/>
       <c r="O242" t="s" s="2">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="P242" t="s" s="2">
         <v>79</v>
@@ -28884,7 +28873,7 @@
         <v>79</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>77</v>
@@ -28902,18 +28891,18 @@
         <v>79</v>
       </c>
       <c r="AL242" t="s" s="2">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="AM242" t="s" s="2">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -28936,17 +28925,17 @@
         <v>88</v>
       </c>
       <c r="K243" t="s" s="2">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="L243" t="s" s="2">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="N243" s="2"/>
       <c r="O243" t="s" s="2">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="P243" t="s" s="2">
         <v>79</v>
@@ -28995,7 +28984,7 @@
         <v>79</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>77</v>
@@ -29013,10 +29002,10 @@
         <v>79</v>
       </c>
       <c r="AL243" t="s" s="2">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="AM243" t="s" s="2">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
   </sheetData>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8427" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8427" uniqueCount="614">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:32:11+00:00</t>
+    <t>2026-06-24T08:54:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -267,8 +267,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}motivationLocaleRequired:La motivation locale doit être renseignée si la motivation de la décision est '9999' (Autre). {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='motivation').valueCodeableConcept.coding.code='215')
- implies ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='motivationLocale').valueString.exists()))}idDecisionMAJCardinality:l'idDecisionMAJ est obligatoire si typeDecision = '5' (Clôture de droit) ou typeDecision ='1' (Attribution) et DroitPrestation.natureDroit = '6' (Renouvellement) ou '7' (Révision). {((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='typeDecision').valueCodeableConcept.coding.code='1') and ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='natureDroitPrestation').valueCodeableConcept=6) or (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='natureDroitPrestation').valueCodeableConcept=7))) implies (identifier.where(type.coding.code='IDDECISIONMAJ').exists())}idDecisionMAJInterdiction:l'idDecisionMAJ n'est pas à transmettre si typeDecision = '1' (Attribution) et DroitPrestation.natureDroit = '1' (Attribution) {((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='typeDecision').valueCodeableConcept.coding.code='1') and (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='natureDroitPrestation').valueCodeableConcept=1)) implies (identifier.where(type.coding.code='IDDECISIONMAJ').exists().not())}FormationCardinality:Formation est obligatoire si le type de droit et prestation est '11.1' (Orientation en Centre de rééducation professionnelle (CRP)). {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='11.1') implies (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='formation').exists())}PrecisionOrientationValues7.8:Si typeDroitPrestation = '7.8' (Orientation vers un Service d'éducation spéciale et de soins à domicile (SESSAD)) alors precisionOrientation = '1' (SESSAD polyvalent) ou '6' (SESSAD pour troubles du langage et des apprentissages). {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='7.8') implies ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=1) and (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=6))}PrecisionOrientationValues7.9:Si typeDroitPrestation = '7.9' (Orientation vers un Service d'accompagnement familial et d'éducation précoce (SAFEP)) alors precisionOrientation = '7' (SAFEP déficience auditive) ou '8' (SAFEP déficience visuelle). {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='7.9') implies ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=7) and (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=8))}PrecisionOrientationValues8.3:Si typeDroitPrestation = '8.3' (Orientation en Enseignement adapté (SEGPA/EREA)) alors precisionOrientation = '9' (Scolarisation en SEGPA (sections d’enseignement général et professionnel adapté)) ou '10' (Scolarisation en EREA (établissements régionaux d’enseignement adapté)). {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.3') implies ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=9) and (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=10))}PrecisionOrientationValues8.6:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) alors precisionOrientation = 'UEA' (Unité d'enseignement élémentaire autisme) ou 'UEM' (Unité d'enseignement en maternelle plan autisme). {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.6') implies ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code='UEA') or (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code='UEM'))}cretonCardinality:Si categorieDroitPrestation = '7' (ESSMS enfant) alors Creton est obligatoire {((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='7') or (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code.matches('^7[.][0-9]+$'))) implies (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='creton').exists())}DateEffetClotureCardinality:Si typeDecision = '5' (Clôture de droit) alors dateEffetCloture est obligatoire. {(extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.where(url='decision').extension.where(url='typeDecision').valueCodeableConcept.coding.code='5') implies ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.where(url='decision').extension.where(url='dateEffetCloture').exists()))}temporaliteAccueilCardinalityViaTypeDroitPrestation:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) ou '8.7' (Orientation vers une Scolarisation en milieu ordinaire à temps partagé) ou '8.8' (Orientation vers une Unité d'enseignement et une scolarisation en ULIS à temps partagé) ou '8.10' (Orientation vers une unité d'enseignement et une scolarisation en enseignement adapté à temps partagé) alors la temporalité d'accueil est obligatoire. {((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.6') or (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.7') or (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.8') or (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.10')) implies (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil').exists())}temporaliteAccueilCardinalityViaCategorieDroitPrestation:Si categorieDroitPrestation = '13' (Orientation ESMS Enfants) ou '7' (Orientation ESMS Adultes) alors la temporalité d'accueil est obligatoire. {((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='13') or (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='7')) implies (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil').exists())}PrecisionOrientationValues13.1-13.2:Si typeDroitPrestation = '13.1' (Orientation vers un établissement d'accueil non médicalisé) ou '13.2' (Orientation vers un établissement d'accueil médicalisé en tout ou partie) alors precisionOrientation est interdit {((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='13.1') or (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='13.2')) implies (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='precisionOrientation').exists().not())}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Decision</t>
@@ -508,6 +507,11 @@
     <t>decision</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}motivationLocaleRequired:La motivation locale doit être renseignée si la motivation de la décision est '9999' (Autre). {(extension.where(url='motivation').valueCodeableConcept.coding.code='9999')
+ implies ((extension.where(url='motivationLocale').valueString.exists()))}DateEffetClotureCardinality:Si typeDecision = '5' (Clôture de droit) alors dateEffetCloture est obligatoire. {(extension.where(url='typeDecision').valueCodeableConcept.coding.code='5') implies ((extension.where(url='dateEffetCloture').exists()))}</t>
+  </si>
+  <si>
     <t>Basic.extension:TDDUIDecision.extension:decision.id</t>
   </si>
   <si>
@@ -700,6 +704,11 @@
   </si>
   <si>
     <t>droitPrestation</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}FormationCardinality:Formation est obligatoire si typeDroitPrestation = '11.1' (Orientation en Centre de rééducation professionnelle (CRP)). {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='11.1') implies (extension.where(url='detailPrestation').extension.where(url='formation').exists())}PrecisionOrientationValues7.8:Si typeDroitPrestation = '7.8' (Orientation vers un Service d'éducation spéciale et de soins à domicile (SESSAD)) alors precisionOrientation entre '1' et
+ '6' {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='7.8') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=1) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=6))}PrecisionOrientationValues7.9:Si typeDroitPrestation = '7.9' (Orientation vers un Service d'accompagnement familial et d'éducation précoce (SAFEP)) alors precisionOrientation entre '7' et '8' {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='7.9') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=7) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=8))}PrecisionOrientationValues13.1-13.2:Si typeDroitPrestation = '13.1' (Orientation vers un établissement d'accueil non médicalisé) ou '13.2' (Orientation vers un établissement d'accueil médicalisé en tout ou partie) alors precisionOrientation est interdit {((extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='13.1') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='13.2')) implies (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').exists().not())}PrecisionOrientationValues8.3:Si typeDroitPrestation = '8.3' (Orientation en Enseignement adapté (SEGPA/EREA)) alors precisionOrientation entre '9' et '10'  {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.3') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=9) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=10))}PrecisionOrientationValues8.6:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) alors precisionOrientation = 'UEA' (Unité d'enseignement élémentaire autisme) ou 'UEM' (Unité d'enseignement en maternelle plan autisme). {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.6') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code='UEA') or (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code='UEM'))}temporaliteAccueilCardinalityViaCategorieDroitPrestation:Si categorieDroitPrestation = '13' (Orientation ESMS Adultes) ou '7' (Orientation ESMS Enfants) alors temporaliteAccueil est obligatoire. {((extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='13') or (extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='7')) implies (extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil').exists())}temporaliteAccueilCardinalityViaTypeDroitPrestation:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) ou '8.7' (Orientation vers une Scolarisation en milieu ordinaire à temps partagé) ou '8.8' (Orientation vers une Unité d'enseignement et une scolarisation en ULIS à temps partagé) ou '8.10' (Orientation vers une unité d'enseignement et une scolarisation en enseignement adapté à temps partagé) alors la temporalité d'accueil est obligatoire. {((extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.6') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.7') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.8') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.10')) implies (extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil').exists())}cretonCardinality:Si categorieDroitPrestation = '7' (ESSMS enfant) alors Creton est obligatoire {((extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='7') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code.matches('^7[.][0-9]+$'))) implies (extension.where(url='creton').exists())}</t>
   </si>
   <si>
     <t>DroitPrestation</t>
@@ -3692,7 +3701,7 @@
         <v>79</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>84</v>
@@ -3706,10 +3715,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3815,10 +3824,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3924,13 +3933,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="B16" t="s" s="2">
-        <v>161</v>
-      </c>
       <c r="C16" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>79</v>
@@ -4024,7 +4033,7 @@
         <v>138</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>79</v>
@@ -4035,10 +4044,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4144,10 +4153,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4253,10 +4262,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4282,13 +4291,13 @@
         <v>101</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4296,7 +4305,7 @@
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>79</v>
@@ -4338,7 +4347,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>87</v>
@@ -4364,10 +4373,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4390,13 +4399,13 @@
         <v>79</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4423,11 +4432,11 @@
         <v>79</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>79</v>
@@ -4445,7 +4454,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -4471,13 +4480,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>79</v>
@@ -4571,7 +4580,7 @@
         <v>138</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>79</v>
@@ -4582,10 +4591,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4691,10 +4700,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4800,10 +4809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4829,13 +4838,13 @@
         <v>101</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4843,7 +4852,7 @@
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>79</v>
@@ -4885,7 +4894,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>87</v>
@@ -4911,10 +4920,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4937,13 +4946,13 @@
         <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4994,7 +5003,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -5020,13 +5029,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>79</v>
@@ -5120,7 +5129,7 @@
         <v>138</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>79</v>
@@ -5131,10 +5140,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5240,10 +5249,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5349,10 +5358,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5378,13 +5387,13 @@
         <v>101</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5392,7 +5401,7 @@
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="S29" t="s" s="2">
         <v>79</v>
@@ -5434,7 +5443,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>87</v>
@@ -5460,10 +5469,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5486,13 +5495,13 @@
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5543,7 +5552,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -5569,13 +5578,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>79</v>
@@ -5669,7 +5678,7 @@
         <v>138</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>79</v>
@@ -5680,10 +5689,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5789,10 +5798,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5898,10 +5907,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5927,13 +5936,13 @@
         <v>101</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5941,7 +5950,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>79</v>
@@ -5983,7 +5992,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>87</v>
@@ -6009,10 +6018,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6035,13 +6044,13 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6068,11 +6077,11 @@
         <v>79</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>79</v>
@@ -6090,7 +6099,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -6116,13 +6125,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>79</v>
@@ -6216,7 +6225,7 @@
         <v>138</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>79</v>
@@ -6227,10 +6236,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6336,10 +6345,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6445,10 +6454,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6474,13 +6483,13 @@
         <v>101</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6488,7 +6497,7 @@
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>79</v>
@@ -6530,7 +6539,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>87</v>
@@ -6556,10 +6565,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6585,10 +6594,10 @@
         <v>147</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6639,7 +6648,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6665,13 +6674,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>79</v>
@@ -6765,7 +6774,7 @@
         <v>138</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>79</v>
@@ -6776,10 +6785,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6885,10 +6894,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6994,10 +7003,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7023,13 +7032,13 @@
         <v>101</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7037,7 +7046,7 @@
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>79</v>
@@ -7079,7 +7088,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>87</v>
@@ -7105,10 +7114,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7134,10 +7143,10 @@
         <v>147</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7188,7 +7197,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -7214,13 +7223,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>79</v>
@@ -7311,10 +7320,10 @@
         <v>79</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>138</v>
+        <v>223</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>79</v>
@@ -7325,10 +7334,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7434,10 +7443,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7445,7 +7454,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>78</v>
@@ -7543,13 +7552,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>79</v>
@@ -7643,7 +7652,7 @@
         <v>138</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>79</v>
@@ -7654,10 +7663,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7763,10 +7772,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7872,10 +7881,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7901,13 +7910,13 @@
         <v>101</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7915,7 +7924,7 @@
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>79</v>
@@ -7957,7 +7966,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>87</v>
@@ -7983,10 +7992,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8009,13 +8018,13 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8042,11 +8051,11 @@
         <v>79</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>79</v>
@@ -8064,7 +8073,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -8090,13 +8099,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>79</v>
@@ -8190,7 +8199,7 @@
         <v>138</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>79</v>
@@ -8201,10 +8210,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8310,10 +8319,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8419,10 +8428,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8448,13 +8457,13 @@
         <v>101</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8462,7 +8471,7 @@
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="S57" t="s" s="2">
         <v>79</v>
@@ -8504,7 +8513,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>87</v>
@@ -8530,10 +8539,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8556,13 +8565,13 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8589,11 +8598,11 @@
         <v>79</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>79</v>
@@ -8611,7 +8620,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8637,13 +8646,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>79</v>
@@ -8737,7 +8746,7 @@
         <v>138</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>79</v>
@@ -8748,10 +8757,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8857,10 +8866,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8966,10 +8975,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8995,13 +9004,13 @@
         <v>101</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9009,7 +9018,7 @@
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>79</v>
@@ -9051,7 +9060,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>87</v>
@@ -9077,10 +9086,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9103,13 +9112,13 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9136,11 +9145,11 @@
         <v>79</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>79</v>
@@ -9158,7 +9167,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -9184,13 +9193,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>79</v>
@@ -9284,7 +9293,7 @@
         <v>138</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>79</v>
@@ -9295,10 +9304,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9404,10 +9413,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9513,10 +9522,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9542,13 +9551,13 @@
         <v>101</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9556,7 +9565,7 @@
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>79</v>
@@ -9598,7 +9607,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>87</v>
@@ -9624,10 +9633,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9650,13 +9659,13 @@
         <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9707,7 +9716,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9733,13 +9742,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>79</v>
@@ -9833,7 +9842,7 @@
         <v>138</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>79</v>
@@ -9844,10 +9853,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9953,10 +9962,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10062,10 +10071,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10091,13 +10100,13 @@
         <v>101</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10105,7 +10114,7 @@
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="S72" t="s" s="2">
         <v>79</v>
@@ -10147,7 +10156,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>87</v>
@@ -10173,10 +10182,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10199,13 +10208,13 @@
         <v>79</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10256,7 +10265,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -10282,13 +10291,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D74" t="s" s="2">
         <v>79</v>
@@ -10382,7 +10391,7 @@
         <v>138</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>79</v>
@@ -10393,10 +10402,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10502,10 +10511,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10611,10 +10620,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10640,13 +10649,13 @@
         <v>101</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10654,7 +10663,7 @@
       </c>
       <c r="Q77" s="2"/>
       <c r="R77" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="S77" t="s" s="2">
         <v>79</v>
@@ -10696,7 +10705,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>87</v>
@@ -10722,10 +10731,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10748,13 +10757,13 @@
         <v>79</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10805,7 +10814,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>77</v>
@@ -10831,13 +10840,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>79</v>
@@ -10931,7 +10940,7 @@
         <v>138</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>79</v>
@@ -10942,10 +10951,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11051,10 +11060,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11160,10 +11169,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11189,13 +11198,13 @@
         <v>101</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11203,7 +11212,7 @@
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="S82" t="s" s="2">
         <v>79</v>
@@ -11245,7 +11254,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>87</v>
@@ -11271,10 +11280,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11297,13 +11306,13 @@
         <v>79</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11330,11 +11339,11 @@
         <v>79</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>79</v>
@@ -11352,7 +11361,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>77</v>
@@ -11378,13 +11387,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>79</v>
@@ -11478,7 +11487,7 @@
         <v>138</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>79</v>
@@ -11489,10 +11498,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11598,10 +11607,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11707,10 +11716,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11736,13 +11745,13 @@
         <v>101</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -11750,7 +11759,7 @@
       </c>
       <c r="Q87" s="2"/>
       <c r="R87" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="S87" t="s" s="2">
         <v>79</v>
@@ -11792,7 +11801,7 @@
         <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>87</v>
@@ -11818,10 +11827,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11844,13 +11853,13 @@
         <v>79</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11901,7 +11910,7 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>77</v>
@@ -11927,13 +11936,13 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D89" t="s" s="2">
         <v>79</v>
@@ -12027,7 +12036,7 @@
         <v>138</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>79</v>
@@ -12038,10 +12047,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12147,10 +12156,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12256,10 +12265,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12285,13 +12294,13 @@
         <v>101</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12299,7 +12308,7 @@
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>79</v>
@@ -12341,7 +12350,7 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>87</v>
@@ -12367,10 +12376,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12393,13 +12402,13 @@
         <v>79</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -12450,7 +12459,7 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>77</v>
@@ -12476,13 +12485,13 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D94" t="s" s="2">
         <v>79</v>
@@ -12576,7 +12585,7 @@
         <v>138</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>79</v>
@@ -12587,10 +12596,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12696,10 +12705,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12805,10 +12814,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12834,13 +12843,13 @@
         <v>101</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -12848,7 +12857,7 @@
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="S97" t="s" s="2">
         <v>79</v>
@@ -12890,7 +12899,7 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>87</v>
@@ -12916,10 +12925,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12942,13 +12951,13 @@
         <v>79</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -12975,11 +12984,11 @@
         <v>79</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>79</v>
@@ -12997,7 +13006,7 @@
         <v>79</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>77</v>
@@ -13023,13 +13032,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>79</v>
@@ -13123,7 +13132,7 @@
         <v>138</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>79</v>
@@ -13134,10 +13143,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13243,10 +13252,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13352,10 +13361,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13381,13 +13390,13 @@
         <v>101</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13395,7 +13404,7 @@
       </c>
       <c r="Q102" s="2"/>
       <c r="R102" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="S102" t="s" s="2">
         <v>79</v>
@@ -13437,7 +13446,7 @@
         <v>79</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>87</v>
@@ -13463,10 +13472,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13492,10 +13501,10 @@
         <v>147</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -13546,7 +13555,7 @@
         <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>77</v>
@@ -13572,13 +13581,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>79</v>
@@ -13672,7 +13681,7 @@
         <v>138</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>79</v>
@@ -13683,10 +13692,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13792,10 +13801,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13901,13 +13910,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>79</v>
@@ -14001,7 +14010,7 @@
         <v>138</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>79</v>
@@ -14012,10 +14021,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14121,10 +14130,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14230,10 +14239,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14259,13 +14268,13 @@
         <v>101</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -14273,7 +14282,7 @@
       </c>
       <c r="Q110" s="2"/>
       <c r="R110" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="S110" t="s" s="2">
         <v>79</v>
@@ -14315,7 +14324,7 @@
         <v>79</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>87</v>
@@ -14341,10 +14350,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14367,13 +14376,13 @@
         <v>79</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -14400,11 +14409,11 @@
         <v>79</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>79</v>
@@ -14422,7 +14431,7 @@
         <v>79</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>77</v>
@@ -14448,13 +14457,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>79</v>
@@ -14548,7 +14557,7 @@
         <v>138</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>79</v>
@@ -14559,10 +14568,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14668,10 +14677,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14777,10 +14786,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14806,13 +14815,13 @@
         <v>101</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -14820,7 +14829,7 @@
       </c>
       <c r="Q115" s="2"/>
       <c r="R115" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="S115" t="s" s="2">
         <v>79</v>
@@ -14862,7 +14871,7 @@
         <v>79</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>87</v>
@@ -14888,10 +14897,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14914,13 +14923,13 @@
         <v>79</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -14947,11 +14956,11 @@
         <v>79</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y116" s="2"/>
       <c r="Z116" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>79</v>
@@ -14969,7 +14978,7 @@
         <v>79</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>77</v>
@@ -14995,13 +15004,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>79</v>
@@ -15095,7 +15104,7 @@
         <v>138</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AL117" t="s" s="2">
         <v>79</v>
@@ -15106,10 +15115,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15215,10 +15224,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15324,10 +15333,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15353,13 +15362,13 @@
         <v>101</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -15367,7 +15376,7 @@
       </c>
       <c r="Q120" s="2"/>
       <c r="R120" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="S120" t="s" s="2">
         <v>79</v>
@@ -15409,7 +15418,7 @@
         <v>79</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>87</v>
@@ -15435,10 +15444,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15461,13 +15470,13 @@
         <v>79</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -15518,7 +15527,7 @@
         <v>79</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>77</v>
@@ -15544,13 +15553,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>79</v>
@@ -15644,7 +15653,7 @@
         <v>138</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>79</v>
@@ -15655,10 +15664,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -15764,10 +15773,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15873,10 +15882,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15902,13 +15911,13 @@
         <v>101</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -15916,7 +15925,7 @@
       </c>
       <c r="Q125" s="2"/>
       <c r="R125" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="S125" t="s" s="2">
         <v>79</v>
@@ -15958,7 +15967,7 @@
         <v>79</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>87</v>
@@ -15984,10 +15993,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16013,10 +16022,10 @@
         <v>147</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -16067,7 +16076,7 @@
         <v>79</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>77</v>
@@ -16093,13 +16102,13 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D127" t="s" s="2">
         <v>79</v>
@@ -16193,7 +16202,7 @@
         <v>138</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>79</v>
@@ -16204,10 +16213,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16313,10 +16322,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16422,10 +16431,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -16451,13 +16460,13 @@
         <v>101</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -16465,7 +16474,7 @@
       </c>
       <c r="Q130" s="2"/>
       <c r="R130" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="S130" t="s" s="2">
         <v>79</v>
@@ -16507,7 +16516,7 @@
         <v>79</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>87</v>
@@ -16533,10 +16542,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16559,13 +16568,13 @@
         <v>79</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -16616,7 +16625,7 @@
         <v>79</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>77</v>
@@ -16642,13 +16651,13 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D132" t="s" s="2">
         <v>79</v>
@@ -16742,7 +16751,7 @@
         <v>138</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AL132" t="s" s="2">
         <v>79</v>
@@ -16753,10 +16762,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -16862,10 +16871,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16971,10 +16980,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17000,13 +17009,13 @@
         <v>101</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -17014,7 +17023,7 @@
       </c>
       <c r="Q135" s="2"/>
       <c r="R135" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="S135" t="s" s="2">
         <v>79</v>
@@ -17056,7 +17065,7 @@
         <v>79</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>87</v>
@@ -17082,10 +17091,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17108,13 +17117,13 @@
         <v>79</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -17165,7 +17174,7 @@
         <v>79</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>77</v>
@@ -17191,13 +17200,13 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>79</v>
@@ -17291,7 +17300,7 @@
         <v>138</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>79</v>
@@ -17302,10 +17311,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -17411,10 +17420,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -17520,10 +17529,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -17549,13 +17558,13 @@
         <v>101</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -17563,7 +17572,7 @@
       </c>
       <c r="Q140" s="2"/>
       <c r="R140" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="S140" t="s" s="2">
         <v>79</v>
@@ -17605,7 +17614,7 @@
         <v>79</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>87</v>
@@ -17631,10 +17640,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -17657,13 +17666,13 @@
         <v>79</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -17690,11 +17699,11 @@
         <v>79</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y141" s="2"/>
       <c r="Z141" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>79</v>
@@ -17712,7 +17721,7 @@
         <v>79</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>77</v>
@@ -17738,13 +17747,13 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D142" t="s" s="2">
         <v>79</v>
@@ -17838,7 +17847,7 @@
         <v>138</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>79</v>
@@ -17849,10 +17858,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -17958,10 +17967,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18067,10 +18076,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18096,13 +18105,13 @@
         <v>101</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
@@ -18110,7 +18119,7 @@
       </c>
       <c r="Q145" s="2"/>
       <c r="R145" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="S145" t="s" s="2">
         <v>79</v>
@@ -18152,7 +18161,7 @@
         <v>79</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>87</v>
@@ -18178,10 +18187,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18204,13 +18213,13 @@
         <v>79</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -18261,7 +18270,7 @@
         <v>79</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>77</v>
@@ -18287,13 +18296,13 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D147" t="s" s="2">
         <v>79</v>
@@ -18387,7 +18396,7 @@
         <v>138</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AL147" t="s" s="2">
         <v>79</v>
@@ -18398,10 +18407,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -18507,14 +18516,14 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
@@ -18536,13 +18545,13 @@
         <v>132</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -18618,13 +18627,13 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D150" t="s" s="2">
         <v>79</v>
@@ -18718,7 +18727,7 @@
         <v>138</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AL150" t="s" s="2">
         <v>79</v>
@@ -18729,10 +18738,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -18838,10 +18847,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -18947,10 +18956,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -18976,13 +18985,13 @@
         <v>101</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -18990,7 +18999,7 @@
       </c>
       <c r="Q153" s="2"/>
       <c r="R153" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="S153" t="s" s="2">
         <v>79</v>
@@ -19032,7 +19041,7 @@
         <v>79</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>87</v>
@@ -19058,10 +19067,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19084,13 +19093,13 @@
         <v>79</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -19117,11 +19126,11 @@
         <v>79</v>
       </c>
       <c r="X154" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y154" s="2"/>
       <c r="Z154" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>79</v>
@@ -19139,7 +19148,7 @@
         <v>79</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>77</v>
@@ -19165,13 +19174,13 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D155" t="s" s="2">
         <v>79</v>
@@ -19265,7 +19274,7 @@
         <v>138</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>79</v>
@@ -19276,10 +19285,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -19385,14 +19394,14 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
@@ -19414,13 +19423,13 @@
         <v>132</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -19496,13 +19505,13 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D158" t="s" s="2">
         <v>79</v>
@@ -19596,7 +19605,7 @@
         <v>138</v>
       </c>
       <c r="AK158" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AL158" t="s" s="2">
         <v>79</v>
@@ -19607,10 +19616,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -19716,10 +19725,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -19825,10 +19834,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -19854,13 +19863,13 @@
         <v>101</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
@@ -19868,7 +19877,7 @@
       </c>
       <c r="Q161" s="2"/>
       <c r="R161" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="S161" t="s" s="2">
         <v>79</v>
@@ -19910,7 +19919,7 @@
         <v>79</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>87</v>
@@ -19936,10 +19945,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -19962,13 +19971,13 @@
         <v>79</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -20019,7 +20028,7 @@
         <v>79</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>77</v>
@@ -20045,13 +20054,13 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D163" t="s" s="2">
         <v>79</v>
@@ -20145,7 +20154,7 @@
         <v>138</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>79</v>
@@ -20156,10 +20165,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -20265,10 +20274,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -20374,10 +20383,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -20403,13 +20412,13 @@
         <v>101</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -20417,7 +20426,7 @@
       </c>
       <c r="Q166" s="2"/>
       <c r="R166" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="S166" t="s" s="2">
         <v>79</v>
@@ -20459,7 +20468,7 @@
         <v>79</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>87</v>
@@ -20485,10 +20494,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -20511,13 +20520,13 @@
         <v>79</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -20568,7 +20577,7 @@
         <v>79</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>77</v>
@@ -20594,13 +20603,13 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D168" t="s" s="2">
         <v>79</v>
@@ -20694,7 +20703,7 @@
         <v>138</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AL168" t="s" s="2">
         <v>79</v>
@@ -20705,10 +20714,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -20814,10 +20823,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -20923,10 +20932,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -20952,13 +20961,13 @@
         <v>101</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -20966,7 +20975,7 @@
       </c>
       <c r="Q171" s="2"/>
       <c r="R171" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="S171" t="s" s="2">
         <v>79</v>
@@ -21008,7 +21017,7 @@
         <v>79</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>87</v>
@@ -21034,10 +21043,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -21060,13 +21069,13 @@
         <v>79</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -21093,11 +21102,11 @@
         <v>79</v>
       </c>
       <c r="X172" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y172" s="2"/>
       <c r="Z172" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AA172" t="s" s="2">
         <v>79</v>
@@ -21115,7 +21124,7 @@
         <v>79</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>77</v>
@@ -21141,10 +21150,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -21170,13 +21179,13 @@
         <v>101</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
@@ -21184,7 +21193,7 @@
       </c>
       <c r="Q173" s="2"/>
       <c r="R173" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="S173" t="s" s="2">
         <v>79</v>
@@ -21226,7 +21235,7 @@
         <v>79</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>87</v>
@@ -21252,10 +21261,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -21278,13 +21287,13 @@
         <v>79</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
@@ -21335,7 +21344,7 @@
         <v>79</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>77</v>
@@ -21361,10 +21370,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -21390,13 +21399,13 @@
         <v>101</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -21404,7 +21413,7 @@
       </c>
       <c r="Q175" s="2"/>
       <c r="R175" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="S175" t="s" s="2">
         <v>79</v>
@@ -21446,7 +21455,7 @@
         <v>79</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>87</v>
@@ -21472,10 +21481,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -21498,13 +21507,13 @@
         <v>79</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -21555,7 +21564,7 @@
         <v>79</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>77</v>
@@ -21581,10 +21590,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -21610,13 +21619,13 @@
         <v>101</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -21624,7 +21633,7 @@
       </c>
       <c r="Q177" s="2"/>
       <c r="R177" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="S177" t="s" s="2">
         <v>79</v>
@@ -21666,7 +21675,7 @@
         <v>79</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>87</v>
@@ -21692,10 +21701,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -21718,13 +21727,13 @@
         <v>79</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" s="2"/>
@@ -21775,7 +21784,7 @@
         <v>79</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>77</v>
@@ -21801,10 +21810,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -21830,13 +21839,13 @@
         <v>101</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O179" s="2"/>
       <c r="P179" t="s" s="2">
@@ -21844,7 +21853,7 @@
       </c>
       <c r="Q179" s="2"/>
       <c r="R179" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="S179" t="s" s="2">
         <v>79</v>
@@ -21886,7 +21895,7 @@
         <v>79</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>87</v>
@@ -21912,10 +21921,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -21938,13 +21947,13 @@
         <v>79</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" s="2"/>
@@ -21995,7 +22004,7 @@
         <v>79</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>77</v>
@@ -22021,10 +22030,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -22050,13 +22059,13 @@
         <v>101</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
@@ -22106,7 +22115,7 @@
         <v>79</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>87</v>
@@ -22132,10 +22141,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -22158,13 +22167,13 @@
         <v>79</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
@@ -22215,7 +22224,7 @@
         <v>79</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>77</v>
@@ -22241,10 +22250,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -22270,13 +22279,13 @@
         <v>101</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
@@ -22284,7 +22293,7 @@
       </c>
       <c r="Q183" s="2"/>
       <c r="R183" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="S183" t="s" s="2">
         <v>79</v>
@@ -22326,7 +22335,7 @@
         <v>79</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>87</v>
@@ -22352,10 +22361,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -22378,13 +22387,13 @@
         <v>79</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
@@ -22435,7 +22444,7 @@
         <v>79</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>77</v>
@@ -22461,14 +22470,14 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E185" s="2"/>
       <c r="F185" t="s" s="2">
@@ -22490,16 +22499,16 @@
         <v>132</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>79</v>
@@ -22548,7 +22557,7 @@
         <v>79</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>77</v>
@@ -22574,10 +22583,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -22600,13 +22609,13 @@
         <v>88</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -22645,7 +22654,7 @@
         <v>79</v>
       </c>
       <c r="AB186" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AC186" s="2"/>
       <c r="AD186" t="s" s="2">
@@ -22655,7 +22664,7 @@
         <v>136</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>77</v>
@@ -22673,18 +22682,18 @@
         <v>79</v>
       </c>
       <c r="AL186" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AM186" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -22790,14 +22799,14 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E188" s="2"/>
       <c r="F188" t="s" s="2">
@@ -22819,13 +22828,13 @@
         <v>132</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
@@ -22901,10 +22910,10 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -22930,16 +22939,16 @@
         <v>107</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="O189" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>79</v>
@@ -22964,13 +22973,13 @@
         <v>79</v>
       </c>
       <c r="X189" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y189" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="Z189" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AA189" t="s" s="2">
         <v>79</v>
@@ -22988,7 +22997,7 @@
         <v>79</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>77</v>
@@ -23006,7 +23015,7 @@
         <v>79</v>
       </c>
       <c r="AL189" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AM189" t="s" s="2">
         <v>79</v>
@@ -23014,10 +23023,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -23040,19 +23049,19 @@
         <v>88</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="O190" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>79</v>
@@ -23077,11 +23086,11 @@
         <v>79</v>
       </c>
       <c r="X190" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y190" s="2"/>
       <c r="Z190" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AA190" t="s" s="2">
         <v>79</v>
@@ -23099,7 +23108,7 @@
         <v>79</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>77</v>
@@ -23117,7 +23126,7 @@
         <v>79</v>
       </c>
       <c r="AL190" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AM190" t="s" s="2">
         <v>79</v>
@@ -23125,10 +23134,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -23154,16 +23163,16 @@
         <v>101</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>79</v>
@@ -23176,7 +23185,7 @@
         <v>79</v>
       </c>
       <c r="T191" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="U191" t="s" s="2">
         <v>79</v>
@@ -23212,7 +23221,7 @@
         <v>79</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>77</v>
@@ -23230,7 +23239,7 @@
         <v>79</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AM191" t="s" s="2">
         <v>79</v>
@@ -23238,10 +23247,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -23267,13 +23276,13 @@
         <v>147</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O192" s="2"/>
       <c r="P192" t="s" s="2">
@@ -23287,7 +23296,7 @@
         <v>79</v>
       </c>
       <c r="T192" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="U192" t="s" s="2">
         <v>79</v>
@@ -23323,7 +23332,7 @@
         <v>79</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>77</v>
@@ -23341,7 +23350,7 @@
         <v>79</v>
       </c>
       <c r="AL192" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AM192" t="s" s="2">
         <v>79</v>
@@ -23349,10 +23358,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -23375,13 +23384,13 @@
         <v>88</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="N193" s="2"/>
       <c r="O193" s="2"/>
@@ -23432,7 +23441,7 @@
         <v>79</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>77</v>
@@ -23450,7 +23459,7 @@
         <v>79</v>
       </c>
       <c r="AL193" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AM193" t="s" s="2">
         <v>79</v>
@@ -23458,10 +23467,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -23484,16 +23493,16 @@
         <v>88</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
@@ -23543,7 +23552,7 @@
         <v>79</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>77</v>
@@ -23561,7 +23570,7 @@
         <v>79</v>
       </c>
       <c r="AL194" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AM194" t="s" s="2">
         <v>79</v>
@@ -23569,13 +23578,13 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D195" t="s" s="2">
         <v>79</v>
@@ -23597,13 +23606,13 @@
         <v>88</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
@@ -23654,7 +23663,7 @@
         <v>79</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>77</v>
@@ -23669,21 +23678,21 @@
         <v>99</v>
       </c>
       <c r="AK195" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AL195" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AM195" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -23789,14 +23798,14 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E197" s="2"/>
       <c r="F197" t="s" s="2">
@@ -23818,13 +23827,13 @@
         <v>132</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
@@ -23900,10 +23909,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -23929,16 +23938,16 @@
         <v>107</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="O198" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="P198" t="s" s="2">
         <v>79</v>
@@ -23963,13 +23972,13 @@
         <v>79</v>
       </c>
       <c r="X198" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y198" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="Z198" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AA198" t="s" s="2">
         <v>79</v>
@@ -23987,7 +23996,7 @@
         <v>79</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>77</v>
@@ -24005,7 +24014,7 @@
         <v>79</v>
       </c>
       <c r="AL198" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AM198" t="s" s="2">
         <v>79</v>
@@ -24013,10 +24022,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -24039,19 +24048,19 @@
         <v>88</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="O199" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="P199" t="s" s="2">
         <v>79</v>
@@ -24061,7 +24070,7 @@
         <v>79</v>
       </c>
       <c r="S199" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="T199" t="s" s="2">
         <v>79</v>
@@ -24076,11 +24085,11 @@
         <v>79</v>
       </c>
       <c r="X199" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y199" s="2"/>
       <c r="Z199" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AA199" t="s" s="2">
         <v>79</v>
@@ -24098,7 +24107,7 @@
         <v>79</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>77</v>
@@ -24116,7 +24125,7 @@
         <v>79</v>
       </c>
       <c r="AL199" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AM199" t="s" s="2">
         <v>79</v>
@@ -24124,10 +24133,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -24153,16 +24162,16 @@
         <v>101</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="O200" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>79</v>
@@ -24175,7 +24184,7 @@
         <v>79</v>
       </c>
       <c r="T200" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="U200" t="s" s="2">
         <v>79</v>
@@ -24211,7 +24220,7 @@
         <v>79</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>77</v>
@@ -24229,7 +24238,7 @@
         <v>79</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AM200" t="s" s="2">
         <v>79</v>
@@ -24237,10 +24246,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -24266,13 +24275,13 @@
         <v>147</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
@@ -24286,7 +24295,7 @@
         <v>79</v>
       </c>
       <c r="T201" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="U201" t="s" s="2">
         <v>79</v>
@@ -24322,7 +24331,7 @@
         <v>79</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>77</v>
@@ -24340,7 +24349,7 @@
         <v>79</v>
       </c>
       <c r="AL201" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AM201" t="s" s="2">
         <v>79</v>
@@ -24348,10 +24357,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -24374,13 +24383,13 @@
         <v>88</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
@@ -24431,7 +24440,7 @@
         <v>79</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>77</v>
@@ -24449,7 +24458,7 @@
         <v>79</v>
       </c>
       <c r="AL202" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AM202" t="s" s="2">
         <v>79</v>
@@ -24457,10 +24466,10 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -24483,16 +24492,16 @@
         <v>88</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="N203" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="O203" s="2"/>
       <c r="P203" t="s" s="2">
@@ -24542,7 +24551,7 @@
         <v>79</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>77</v>
@@ -24560,7 +24569,7 @@
         <v>79</v>
       </c>
       <c r="AL203" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AM203" t="s" s="2">
         <v>79</v>
@@ -24568,13 +24577,13 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D204" t="s" s="2">
         <v>79</v>
@@ -24596,13 +24605,13 @@
         <v>88</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="N204" s="2"/>
       <c r="O204" s="2"/>
@@ -24653,7 +24662,7 @@
         <v>79</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>77</v>
@@ -24668,21 +24677,21 @@
         <v>99</v>
       </c>
       <c r="AK204" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AL204" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AM204" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -24788,14 +24797,14 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E206" s="2"/>
       <c r="F206" t="s" s="2">
@@ -24817,13 +24826,13 @@
         <v>132</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="O206" s="2"/>
       <c r="P206" t="s" s="2">
@@ -24899,10 +24908,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -24928,16 +24937,16 @@
         <v>107</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N207" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="O207" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="P207" t="s" s="2">
         <v>79</v>
@@ -24962,13 +24971,13 @@
         <v>79</v>
       </c>
       <c r="X207" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y207" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="Z207" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AA207" t="s" s="2">
         <v>79</v>
@@ -24986,7 +24995,7 @@
         <v>79</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>77</v>
@@ -25004,7 +25013,7 @@
         <v>79</v>
       </c>
       <c r="AL207" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AM207" t="s" s="2">
         <v>79</v>
@@ -25012,10 +25021,10 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -25038,19 +25047,19 @@
         <v>88</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="O208" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="P208" t="s" s="2">
         <v>79</v>
@@ -25060,7 +25069,7 @@
         <v>79</v>
       </c>
       <c r="S208" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="T208" t="s" s="2">
         <v>79</v>
@@ -25075,11 +25084,11 @@
         <v>79</v>
       </c>
       <c r="X208" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y208" s="2"/>
       <c r="Z208" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AA208" t="s" s="2">
         <v>79</v>
@@ -25097,7 +25106,7 @@
         <v>79</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>77</v>
@@ -25115,7 +25124,7 @@
         <v>79</v>
       </c>
       <c r="AL208" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AM208" t="s" s="2">
         <v>79</v>
@@ -25123,10 +25132,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -25152,16 +25161,16 @@
         <v>101</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="O209" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="P209" t="s" s="2">
         <v>79</v>
@@ -25174,7 +25183,7 @@
         <v>79</v>
       </c>
       <c r="T209" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="U209" t="s" s="2">
         <v>79</v>
@@ -25210,7 +25219,7 @@
         <v>79</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>77</v>
@@ -25228,7 +25237,7 @@
         <v>79</v>
       </c>
       <c r="AL209" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AM209" t="s" s="2">
         <v>79</v>
@@ -25236,10 +25245,10 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -25265,13 +25274,13 @@
         <v>147</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
@@ -25285,7 +25294,7 @@
         <v>79</v>
       </c>
       <c r="T210" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="U210" t="s" s="2">
         <v>79</v>
@@ -25321,7 +25330,7 @@
         <v>79</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>77</v>
@@ -25339,7 +25348,7 @@
         <v>79</v>
       </c>
       <c r="AL210" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AM210" t="s" s="2">
         <v>79</v>
@@ -25347,10 +25356,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -25373,13 +25382,13 @@
         <v>88</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="N211" s="2"/>
       <c r="O211" s="2"/>
@@ -25430,7 +25439,7 @@
         <v>79</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>77</v>
@@ -25448,7 +25457,7 @@
         <v>79</v>
       </c>
       <c r="AL211" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AM211" t="s" s="2">
         <v>79</v>
@@ -25456,10 +25465,10 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -25482,16 +25491,16 @@
         <v>88</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="N212" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
@@ -25541,7 +25550,7 @@
         <v>79</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>77</v>
@@ -25559,7 +25568,7 @@
         <v>79</v>
       </c>
       <c r="AL212" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AM212" t="s" s="2">
         <v>79</v>
@@ -25567,13 +25576,13 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D213" t="s" s="2">
         <v>79</v>
@@ -25595,13 +25604,13 @@
         <v>88</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="N213" s="2"/>
       <c r="O213" s="2"/>
@@ -25652,7 +25661,7 @@
         <v>79</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>77</v>
@@ -25667,21 +25676,21 @@
         <v>99</v>
       </c>
       <c r="AK213" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AL213" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AM213" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -25787,14 +25796,14 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E215" s="2"/>
       <c r="F215" t="s" s="2">
@@ -25816,13 +25825,13 @@
         <v>132</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N215" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
@@ -25898,10 +25907,10 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -25927,16 +25936,16 @@
         <v>107</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="O216" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="P216" t="s" s="2">
         <v>79</v>
@@ -25961,13 +25970,13 @@
         <v>79</v>
       </c>
       <c r="X216" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y216" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="Z216" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AA216" t="s" s="2">
         <v>79</v>
@@ -25985,7 +25994,7 @@
         <v>79</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>77</v>
@@ -26003,7 +26012,7 @@
         <v>79</v>
       </c>
       <c r="AL216" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AM216" t="s" s="2">
         <v>79</v>
@@ -26011,10 +26020,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -26037,19 +26046,19 @@
         <v>88</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="N217" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="O217" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>79</v>
@@ -26059,7 +26068,7 @@
         <v>79</v>
       </c>
       <c r="S217" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="T217" t="s" s="2">
         <v>79</v>
@@ -26074,11 +26083,11 @@
         <v>79</v>
       </c>
       <c r="X217" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y217" s="2"/>
       <c r="Z217" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AA217" t="s" s="2">
         <v>79</v>
@@ -26096,7 +26105,7 @@
         <v>79</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>77</v>
@@ -26114,7 +26123,7 @@
         <v>79</v>
       </c>
       <c r="AL217" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AM217" t="s" s="2">
         <v>79</v>
@@ -26122,10 +26131,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -26151,16 +26160,16 @@
         <v>101</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="N218" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="O218" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="P218" t="s" s="2">
         <v>79</v>
@@ -26170,10 +26179,10 @@
         <v>79</v>
       </c>
       <c r="S218" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="T218" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="U218" t="s" s="2">
         <v>79</v>
@@ -26209,7 +26218,7 @@
         <v>79</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>77</v>
@@ -26227,7 +26236,7 @@
         <v>79</v>
       </c>
       <c r="AL218" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AM218" t="s" s="2">
         <v>79</v>
@@ -26235,10 +26244,10 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -26264,13 +26273,13 @@
         <v>147</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="N219" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O219" s="2"/>
       <c r="P219" t="s" s="2">
@@ -26284,7 +26293,7 @@
         <v>79</v>
       </c>
       <c r="T219" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="U219" t="s" s="2">
         <v>79</v>
@@ -26320,7 +26329,7 @@
         <v>79</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>77</v>
@@ -26338,7 +26347,7 @@
         <v>79</v>
       </c>
       <c r="AL219" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AM219" t="s" s="2">
         <v>79</v>
@@ -26346,10 +26355,10 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -26372,13 +26381,13 @@
         <v>88</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="N220" s="2"/>
       <c r="O220" s="2"/>
@@ -26429,7 +26438,7 @@
         <v>79</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>77</v>
@@ -26447,7 +26456,7 @@
         <v>79</v>
       </c>
       <c r="AL220" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AM220" t="s" s="2">
         <v>79</v>
@@ -26455,10 +26464,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -26481,16 +26490,16 @@
         <v>88</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="N221" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="O221" s="2"/>
       <c r="P221" t="s" s="2">
@@ -26540,7 +26549,7 @@
         <v>79</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>77</v>
@@ -26558,7 +26567,7 @@
         <v>79</v>
       </c>
       <c r="AL221" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AM221" t="s" s="2">
         <v>79</v>
@@ -26566,13 +26575,13 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D222" t="s" s="2">
         <v>79</v>
@@ -26594,13 +26603,13 @@
         <v>88</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" s="2"/>
@@ -26651,7 +26660,7 @@
         <v>79</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>77</v>
@@ -26666,21 +26675,21 @@
         <v>99</v>
       </c>
       <c r="AK222" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AL222" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AM222" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -26786,14 +26795,14 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E224" s="2"/>
       <c r="F224" t="s" s="2">
@@ -26815,13 +26824,13 @@
         <v>132</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N224" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="O224" s="2"/>
       <c r="P224" t="s" s="2">
@@ -26897,10 +26906,10 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -26926,16 +26935,16 @@
         <v>107</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N225" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="O225" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="P225" t="s" s="2">
         <v>79</v>
@@ -26960,13 +26969,13 @@
         <v>79</v>
       </c>
       <c r="X225" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y225" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="Z225" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AA225" t="s" s="2">
         <v>79</v>
@@ -26984,7 +26993,7 @@
         <v>79</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>77</v>
@@ -27002,7 +27011,7 @@
         <v>79</v>
       </c>
       <c r="AL225" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AM225" t="s" s="2">
         <v>79</v>
@@ -27010,10 +27019,10 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -27036,19 +27045,19 @@
         <v>88</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="N226" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="O226" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="P226" t="s" s="2">
         <v>79</v>
@@ -27058,7 +27067,7 @@
         <v>79</v>
       </c>
       <c r="S226" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="T226" t="s" s="2">
         <v>79</v>
@@ -27073,11 +27082,11 @@
         <v>79</v>
       </c>
       <c r="X226" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y226" s="2"/>
       <c r="Z226" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AA226" t="s" s="2">
         <v>79</v>
@@ -27095,7 +27104,7 @@
         <v>79</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>77</v>
@@ -27113,7 +27122,7 @@
         <v>79</v>
       </c>
       <c r="AL226" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AM226" t="s" s="2">
         <v>79</v>
@@ -27121,10 +27130,10 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -27150,16 +27159,16 @@
         <v>101</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="N227" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="O227" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="P227" t="s" s="2">
         <v>79</v>
@@ -27169,10 +27178,10 @@
         <v>79</v>
       </c>
       <c r="S227" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="T227" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="U227" t="s" s="2">
         <v>79</v>
@@ -27208,7 +27217,7 @@
         <v>79</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>77</v>
@@ -27226,7 +27235,7 @@
         <v>79</v>
       </c>
       <c r="AL227" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AM227" t="s" s="2">
         <v>79</v>
@@ -27234,10 +27243,10 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -27263,13 +27272,13 @@
         <v>147</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="N228" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O228" s="2"/>
       <c r="P228" t="s" s="2">
@@ -27283,7 +27292,7 @@
         <v>79</v>
       </c>
       <c r="T228" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="U228" t="s" s="2">
         <v>79</v>
@@ -27319,7 +27328,7 @@
         <v>79</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>77</v>
@@ -27337,7 +27346,7 @@
         <v>79</v>
       </c>
       <c r="AL228" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AM228" t="s" s="2">
         <v>79</v>
@@ -27345,10 +27354,10 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -27371,13 +27380,13 @@
         <v>88</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -27428,7 +27437,7 @@
         <v>79</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>77</v>
@@ -27446,7 +27455,7 @@
         <v>79</v>
       </c>
       <c r="AL229" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AM229" t="s" s="2">
         <v>79</v>
@@ -27454,10 +27463,10 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -27480,16 +27489,16 @@
         <v>88</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="N230" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="O230" s="2"/>
       <c r="P230" t="s" s="2">
@@ -27539,7 +27548,7 @@
         <v>79</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>77</v>
@@ -27557,7 +27566,7 @@
         <v>79</v>
       </c>
       <c r="AL230" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AM230" t="s" s="2">
         <v>79</v>
@@ -27565,13 +27574,13 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D231" t="s" s="2">
         <v>79</v>
@@ -27593,13 +27602,13 @@
         <v>88</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="N231" s="2"/>
       <c r="O231" s="2"/>
@@ -27650,7 +27659,7 @@
         <v>79</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>77</v>
@@ -27665,21 +27674,21 @@
         <v>99</v>
       </c>
       <c r="AK231" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AL231" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AM231" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -27785,14 +27794,14 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E233" s="2"/>
       <c r="F233" t="s" s="2">
@@ -27814,13 +27823,13 @@
         <v>132</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N233" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="O233" s="2"/>
       <c r="P233" t="s" s="2">
@@ -27896,10 +27905,10 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -27925,16 +27934,16 @@
         <v>107</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N234" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="O234" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="P234" t="s" s="2">
         <v>79</v>
@@ -27959,13 +27968,13 @@
         <v>79</v>
       </c>
       <c r="X234" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y234" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="Z234" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AA234" t="s" s="2">
         <v>79</v>
@@ -27983,7 +27992,7 @@
         <v>79</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>77</v>
@@ -28001,7 +28010,7 @@
         <v>79</v>
       </c>
       <c r="AL234" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AM234" t="s" s="2">
         <v>79</v>
@@ -28009,10 +28018,10 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -28035,19 +28044,19 @@
         <v>88</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="N235" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="O235" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="P235" t="s" s="2">
         <v>79</v>
@@ -28057,7 +28066,7 @@
         <v>79</v>
       </c>
       <c r="S235" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="T235" t="s" s="2">
         <v>79</v>
@@ -28072,11 +28081,11 @@
         <v>79</v>
       </c>
       <c r="X235" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y235" s="2"/>
       <c r="Z235" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AA235" t="s" s="2">
         <v>79</v>
@@ -28094,7 +28103,7 @@
         <v>79</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>77</v>
@@ -28112,7 +28121,7 @@
         <v>79</v>
       </c>
       <c r="AL235" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AM235" t="s" s="2">
         <v>79</v>
@@ -28120,10 +28129,10 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -28149,16 +28158,16 @@
         <v>101</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="N236" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="O236" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="P236" t="s" s="2">
         <v>79</v>
@@ -28168,10 +28177,10 @@
         <v>79</v>
       </c>
       <c r="S236" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="T236" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="U236" t="s" s="2">
         <v>79</v>
@@ -28207,7 +28216,7 @@
         <v>79</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>77</v>
@@ -28225,7 +28234,7 @@
         <v>79</v>
       </c>
       <c r="AL236" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AM236" t="s" s="2">
         <v>79</v>
@@ -28233,10 +28242,10 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -28262,13 +28271,13 @@
         <v>147</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="N237" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O237" s="2"/>
       <c r="P237" t="s" s="2">
@@ -28282,7 +28291,7 @@
         <v>79</v>
       </c>
       <c r="T237" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="U237" t="s" s="2">
         <v>79</v>
@@ -28318,7 +28327,7 @@
         <v>79</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>77</v>
@@ -28336,7 +28345,7 @@
         <v>79</v>
       </c>
       <c r="AL237" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AM237" t="s" s="2">
         <v>79</v>
@@ -28344,10 +28353,10 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -28370,13 +28379,13 @@
         <v>88</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="N238" s="2"/>
       <c r="O238" s="2"/>
@@ -28427,7 +28436,7 @@
         <v>79</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>77</v>
@@ -28445,7 +28454,7 @@
         <v>79</v>
       </c>
       <c r="AL238" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AM238" t="s" s="2">
         <v>79</v>
@@ -28453,10 +28462,10 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -28479,16 +28488,16 @@
         <v>88</v>
       </c>
       <c r="K239" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="N239" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="O239" s="2"/>
       <c r="P239" t="s" s="2">
@@ -28538,7 +28547,7 @@
         <v>79</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>77</v>
@@ -28556,7 +28565,7 @@
         <v>79</v>
       </c>
       <c r="AL239" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AM239" t="s" s="2">
         <v>79</v>
@@ -28564,10 +28573,10 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -28590,19 +28599,19 @@
         <v>88</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="N240" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="O240" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="P240" t="s" s="2">
         <v>79</v>
@@ -28612,7 +28621,7 @@
         <v>79</v>
       </c>
       <c r="S240" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="T240" t="s" s="2">
         <v>79</v>
@@ -28627,11 +28636,11 @@
         <v>79</v>
       </c>
       <c r="X240" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y240" s="2"/>
       <c r="Z240" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AA240" t="s" s="2">
         <v>79</v>
@@ -28649,7 +28658,7 @@
         <v>79</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>87</v>
@@ -28667,18 +28676,18 @@
         <v>79</v>
       </c>
       <c r="AL240" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AM240" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -28701,19 +28710,19 @@
         <v>88</v>
       </c>
       <c r="K241" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="N241" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="O241" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="P241" t="s" s="2">
         <v>79</v>
@@ -28762,7 +28771,7 @@
         <v>79</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>77</v>
@@ -28777,21 +28786,21 @@
         <v>99</v>
       </c>
       <c r="AK241" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AL241" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AM241" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -28814,17 +28823,17 @@
         <v>88</v>
       </c>
       <c r="K242" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L242" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="N242" s="2"/>
       <c r="O242" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="P242" t="s" s="2">
         <v>79</v>
@@ -28873,7 +28882,7 @@
         <v>79</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>77</v>
@@ -28891,18 +28900,18 @@
         <v>79</v>
       </c>
       <c r="AL242" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AM242" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -28925,17 +28934,17 @@
         <v>88</v>
       </c>
       <c r="K243" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="L243" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="N243" s="2"/>
       <c r="O243" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="P243" t="s" s="2">
         <v>79</v>
@@ -28984,7 +28993,7 @@
         <v>79</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>77</v>
@@ -29002,10 +29011,10 @@
         <v>79</v>
       </c>
       <c r="AL243" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AM243" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
   </sheetData>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T08:54:25+00:00</t>
+    <t>2026-06-24T09:36:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8427" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8427" uniqueCount="613">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T09:36:36+00:00</t>
+    <t>2026-06-24T12:11:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1645,9 +1645,6 @@
   </si>
   <si>
     <t>idDecisionMAJ</t>
-  </si>
-  <si>
-    <t>Identifiant révisé de la décision</t>
   </si>
   <si>
     <t>Decision.idDecisionMAJ</t>
@@ -24608,7 +24605,7 @@
         <v>462</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>530</v>
+        <v>516</v>
       </c>
       <c r="M204" t="s" s="2">
         <v>464</v>
@@ -24677,7 +24674,7 @@
         <v>99</v>
       </c>
       <c r="AK204" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AL204" t="s" s="2">
         <v>466</v>
@@ -24688,7 +24685,7 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B205" t="s" s="2">
         <v>468</v>
@@ -24797,7 +24794,7 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B206" t="s" s="2">
         <v>469</v>
@@ -24908,7 +24905,7 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B207" t="s" s="2">
         <v>470</v>
@@ -25021,7 +25018,7 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B208" t="s" s="2">
         <v>479</v>
@@ -25069,7 +25066,7 @@
         <v>79</v>
       </c>
       <c r="S208" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="T208" t="s" s="2">
         <v>79</v>
@@ -25132,7 +25129,7 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B209" t="s" s="2">
         <v>486</v>
@@ -25245,7 +25242,7 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B210" t="s" s="2">
         <v>494</v>
@@ -25356,7 +25353,7 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B211" t="s" s="2">
         <v>501</v>
@@ -25465,7 +25462,7 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B212" t="s" s="2">
         <v>507</v>
@@ -25576,13 +25573,13 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B213" t="s" s="2">
         <v>461</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D213" t="s" s="2">
         <v>79</v>
@@ -25607,7 +25604,7 @@
         <v>462</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="M213" t="s" s="2">
         <v>464</v>
@@ -25676,7 +25673,7 @@
         <v>99</v>
       </c>
       <c r="AK213" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AL213" t="s" s="2">
         <v>466</v>
@@ -25687,7 +25684,7 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B214" t="s" s="2">
         <v>468</v>
@@ -25796,7 +25793,7 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B215" t="s" s="2">
         <v>469</v>
@@ -25907,7 +25904,7 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B216" t="s" s="2">
         <v>470</v>
@@ -26020,7 +26017,7 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B217" t="s" s="2">
         <v>479</v>
@@ -26068,7 +26065,7 @@
         <v>79</v>
       </c>
       <c r="S217" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="T217" t="s" s="2">
         <v>79</v>
@@ -26131,7 +26128,7 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B218" t="s" s="2">
         <v>486</v>
@@ -26179,7 +26176,7 @@
         <v>79</v>
       </c>
       <c r="S218" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="T218" t="s" s="2">
         <v>491</v>
@@ -26244,7 +26241,7 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B219" t="s" s="2">
         <v>494</v>
@@ -26355,7 +26352,7 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B220" t="s" s="2">
         <v>501</v>
@@ -26464,7 +26461,7 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B221" t="s" s="2">
         <v>507</v>
@@ -26575,13 +26572,13 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B222" t="s" s="2">
         <v>461</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D222" t="s" s="2">
         <v>79</v>
@@ -26606,7 +26603,7 @@
         <v>462</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="M222" t="s" s="2">
         <v>464</v>
@@ -26675,7 +26672,7 @@
         <v>99</v>
       </c>
       <c r="AK222" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AL222" t="s" s="2">
         <v>466</v>
@@ -26686,7 +26683,7 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B223" t="s" s="2">
         <v>468</v>
@@ -26795,7 +26792,7 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B224" t="s" s="2">
         <v>469</v>
@@ -26906,7 +26903,7 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B225" t="s" s="2">
         <v>470</v>
@@ -27019,7 +27016,7 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B226" t="s" s="2">
         <v>479</v>
@@ -27067,7 +27064,7 @@
         <v>79</v>
       </c>
       <c r="S226" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="T226" t="s" s="2">
         <v>79</v>
@@ -27130,7 +27127,7 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B227" t="s" s="2">
         <v>486</v>
@@ -27178,7 +27175,7 @@
         <v>79</v>
       </c>
       <c r="S227" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="T227" t="s" s="2">
         <v>491</v>
@@ -27243,7 +27240,7 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B228" t="s" s="2">
         <v>494</v>
@@ -27354,7 +27351,7 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B229" t="s" s="2">
         <v>501</v>
@@ -27463,7 +27460,7 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B230" t="s" s="2">
         <v>507</v>
@@ -27574,13 +27571,13 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B231" t="s" s="2">
         <v>461</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D231" t="s" s="2">
         <v>79</v>
@@ -27605,7 +27602,7 @@
         <v>462</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="M231" t="s" s="2">
         <v>464</v>
@@ -27674,7 +27671,7 @@
         <v>99</v>
       </c>
       <c r="AK231" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AL231" t="s" s="2">
         <v>466</v>
@@ -27685,7 +27682,7 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B232" t="s" s="2">
         <v>468</v>
@@ -27794,7 +27791,7 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B233" t="s" s="2">
         <v>469</v>
@@ -27905,7 +27902,7 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B234" t="s" s="2">
         <v>470</v>
@@ -28018,7 +28015,7 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B235" t="s" s="2">
         <v>479</v>
@@ -28066,7 +28063,7 @@
         <v>79</v>
       </c>
       <c r="S235" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="T235" t="s" s="2">
         <v>79</v>
@@ -28129,7 +28126,7 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B236" t="s" s="2">
         <v>486</v>
@@ -28177,7 +28174,7 @@
         <v>79</v>
       </c>
       <c r="S236" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="T236" t="s" s="2">
         <v>491</v>
@@ -28242,7 +28239,7 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B237" t="s" s="2">
         <v>494</v>
@@ -28353,7 +28350,7 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B238" t="s" s="2">
         <v>501</v>
@@ -28462,7 +28459,7 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B239" t="s" s="2">
         <v>507</v>
@@ -28573,10 +28570,10 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -28602,16 +28599,16 @@
         <v>178</v>
       </c>
       <c r="L240" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="M240" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="M240" t="s" s="2">
+      <c r="N240" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="N240" t="s" s="2">
+      <c r="O240" t="s" s="2">
         <v>586</v>
-      </c>
-      <c r="O240" t="s" s="2">
-        <v>587</v>
       </c>
       <c r="P240" t="s" s="2">
         <v>79</v>
@@ -28621,7 +28618,7 @@
         <v>79</v>
       </c>
       <c r="S240" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="T240" t="s" s="2">
         <v>79</v>
@@ -28640,7 +28637,7 @@
       </c>
       <c r="Y240" s="2"/>
       <c r="Z240" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AA240" t="s" s="2">
         <v>79</v>
@@ -28658,7 +28655,7 @@
         <v>79</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>87</v>
@@ -28676,18 +28673,18 @@
         <v>79</v>
       </c>
       <c r="AL240" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AM240" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="AM240" t="s" s="2">
-        <v>591</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -28710,19 +28707,19 @@
         <v>88</v>
       </c>
       <c r="K241" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="L241" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="L241" t="s" s="2">
+      <c r="M241" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="M241" t="s" s="2">
+      <c r="N241" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="N241" t="s" s="2">
+      <c r="O241" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="O241" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="P241" t="s" s="2">
         <v>79</v>
@@ -28771,7 +28768,7 @@
         <v>79</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>77</v>
@@ -28786,21 +28783,21 @@
         <v>99</v>
       </c>
       <c r="AK241" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AL241" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="AL241" t="s" s="2">
+      <c r="AM241" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="AM241" t="s" s="2">
-        <v>600</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -28826,14 +28823,14 @@
         <v>191</v>
       </c>
       <c r="L242" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M242" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="M242" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="N242" s="2"/>
       <c r="O242" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="P242" t="s" s="2">
         <v>79</v>
@@ -28882,7 +28879,7 @@
         <v>79</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>77</v>
@@ -28900,18 +28897,18 @@
         <v>79</v>
       </c>
       <c r="AL242" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AM242" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="AM242" t="s" s="2">
-        <v>606</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -28934,17 +28931,17 @@
         <v>88</v>
       </c>
       <c r="K243" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="L243" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="L243" t="s" s="2">
+      <c r="M243" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="M243" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="N243" s="2"/>
       <c r="O243" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P243" t="s" s="2">
         <v>79</v>
@@ -28993,7 +28990,7 @@
         <v>79</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>77</v>
@@ -29011,10 +29008,10 @@
         <v>79</v>
       </c>
       <c r="AL243" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="AM243" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="AM243" t="s" s="2">
-        <v>613</v>
       </c>
     </row>
   </sheetData>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T12:11:25+00:00</t>
+    <t>2026-06-24T12:16:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -267,7 +267,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}idDecisionMAJCardinality:L'idDecisionMAJ est obligatoire si typeDecision = '5' (Clôture de droit) ou typeDecision ='1' (Attribution) et DroitPrestation.natureDroit = '6' (Renouvellement) ou '7' (Révision). {((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='typeDecision').valueCodeableConcept.coding.code='1') and ((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='natureDroitPrestation').valueCodeableConcept=6) or (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='natureDroitPrestation').valueCodeableConcept=7))) implies (identifier.where(type.coding.code='IDDECISIONMAJ').exists())}idDecisionMAJInterdiction:L'idDecisionMAJ n'est pas à transmettre si typeDecision = '1' (Attribution) et DroitPrestation.natureDroit = '1' (Attribution) {((extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='typeDecision').valueCodeableConcept.coding.code='1') and (extension.where(url='https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-decision').extension.extension.where(url='droitPrestation').extension.where(url='natureDroitPrestation').valueCodeableConcept=1)) implies (identifier.where(type.coding.code='IDDECISIONMAJ').exists().not())}</t>
   </si>
   <si>
     <t>Decision</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T08:27:57+00:00</t>
+    <t>2026-06-25T09:12:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -502,7 +502,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}motivationLocaleRequired:La motivation locale doit être renseignée si la motivation de la décision est '9999' (Autre). {(extension.where(url='motivation').valueCodeableConcept.coding.code='9999') implies ((extension.where(url='motivationLocale').valueString.exists()))}DateEffetClotureCardinality:Si typeDecision = '5' (Clôture de droit) alors dateEffetCloture est obligatoire. {(extension.where(url='typeDecision').valueCodeableConcept.coding.code='5') implies ((extension.where(url='dateEffetCloture').exists()))}</t>
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}motivationLocaleRequired:La motivation locale doit être renseignée si la motivation de la décision est '9999' (Autre). {(where(url='motivation').valueCodeableConcept.coding.code='9999') implies ((where(url='motivationLocale').valueString.exists()))}DateEffetClotureCardinality:Si typeDecision = '5' (Clôture de droit) alors dateEffetCloture est obligatoire. {(extension.where(url='typeDecision').valueCodeableConcept.coding.code='5') implies ((extension.where(url='dateEffetCloture').exists()))}</t>
   </si>
   <si>
     <t>Basic.extension:TDDUIDecision.extension:typeDecision</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T09:12:27+00:00</t>
+    <t>2026-06-25T09:43:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -502,7 +502,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}motivationLocaleRequired:La motivation locale doit être renseignée si la motivation de la décision est '9999' (Autre). {(where(url='motivation').valueCodeableConcept.coding.code='9999') implies ((where(url='motivationLocale').valueString.exists()))}DateEffetClotureCardinality:Si typeDecision = '5' (Clôture de droit) alors dateEffetCloture est obligatoire. {(extension.where(url='typeDecision').valueCodeableConcept.coding.code='5') implies ((extension.where(url='dateEffetCloture').exists()))}</t>
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}motivationLocaleRequired:La motivation locale doit être renseignée si la motivation de la décision est '9999' (Autre). {extension.where(url='motivation').valueCodeableConcept.coding.where(code='9999').exists() implies extension.where(url='motivationLocale').valueString.exists()}DateEffetClotureCardinality:Si typeDecision = '5' (Clôture de droit) alors dateEffetCloture est obligatoire. {(extension.where(url='typeDecision').valueCodeableConcept.coding.code='5') implies ((extension.where(url='dateEffetCloture').exists()))}</t>
   </si>
   <si>
     <t>Basic.extension:TDDUIDecision.extension:typeDecision</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T09:43:13+00:00</t>
+    <t>2026-06-25T10:03:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -467,6 +467,10 @@
 </t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}motivationLocaleRequired:La motivation locale doit être renseignée si la motivation de la décision est '9999' (Autre). {(extension.where(url='motivation').valueCodeableConcept.coding.where(code='9999').exists()) implies (extension.where(url='motivationLocale').valueString.exists())}DateEffetClotureCardinality:Si typeDecision = '5' (Clôture de droit) alors dateEffetCloture est obligatoire. {(extension.where(url='typeDecision').valueCodeableConcept.coding.code='5'.exists()) implies (extension.where(url='dateEffetCloture').exists())}</t>
+  </si>
+  <si>
     <t>Basic.extension:TDDUIDecision.id</t>
   </si>
   <si>
@@ -499,10 +503,6 @@
   </si>
   <si>
     <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}motivationLocaleRequired:La motivation locale doit être renseignée si la motivation de la décision est '9999' (Autre). {extension.where(url='motivation').valueCodeableConcept.coding.where(code='9999').exists() implies extension.where(url='motivationLocale').valueString.exists()}DateEffetClotureCardinality:Si typeDecision = '5' (Clôture de droit) alors dateEffetCloture est obligatoire. {(extension.where(url='typeDecision').valueCodeableConcept.coding.code='5') implies ((extension.where(url='dateEffetCloture').exists()))}</t>
   </si>
   <si>
     <t>Basic.extension:TDDUIDecision.extension:typeDecision</t>
@@ -3338,7 +3338,7 @@
         <v>144</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>84</v>
@@ -3352,10 +3352,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3378,13 +3378,13 @@
         <v>79</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3435,7 +3435,7 @@
         <v>79</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -3453,7 +3453,7 @@
         <v>79</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>79</v>
@@ -3461,10 +3461,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3535,7 +3535,7 @@
         <v>135</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>79</v>
@@ -3544,7 +3544,7 @@
         <v>136</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -3556,7 +3556,7 @@
         <v>79</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>79</v>
@@ -3573,7 +3573,7 @@
         <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C13" t="s" s="2">
         <v>158</v>
@@ -3655,7 +3655,7 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -3707,13 +3707,13 @@
         <v>79</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3764,7 +3764,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3782,7 +3782,7 @@
         <v>79</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>79</v>
@@ -3864,7 +3864,7 @@
         <v>135</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>79</v>
@@ -3873,7 +3873,7 @@
         <v>136</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -4120,7 +4120,7 @@
         <v>178</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C18" t="s" s="2">
         <v>179</v>
@@ -4202,7 +4202,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -4254,13 +4254,13 @@
         <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4311,7 +4311,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -4329,7 +4329,7 @@
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>79</v>
@@ -4411,7 +4411,7 @@
         <v>135</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>79</v>
@@ -4420,7 +4420,7 @@
         <v>136</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -4669,7 +4669,7 @@
         <v>186</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C23" t="s" s="2">
         <v>187</v>
@@ -4751,7 +4751,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4803,13 +4803,13 @@
         <v>79</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4860,7 +4860,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4878,7 +4878,7 @@
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>79</v>
@@ -4960,7 +4960,7 @@
         <v>135</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>79</v>
@@ -4969,7 +4969,7 @@
         <v>136</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -5218,7 +5218,7 @@
         <v>193</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C28" t="s" s="2">
         <v>194</v>
@@ -5300,7 +5300,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -5352,13 +5352,13 @@
         <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5409,7 +5409,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -5427,7 +5427,7 @@
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>79</v>
@@ -5509,7 +5509,7 @@
         <v>135</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>79</v>
@@ -5518,7 +5518,7 @@
         <v>136</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -5765,7 +5765,7 @@
         <v>201</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C33" t="s" s="2">
         <v>202</v>
@@ -5847,7 +5847,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5899,13 +5899,13 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5956,7 +5956,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5974,7 +5974,7 @@
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>79</v>
@@ -6056,7 +6056,7 @@
         <v>135</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>79</v>
@@ -6065,7 +6065,7 @@
         <v>136</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -6228,7 +6228,7 @@
         <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>173</v>
@@ -6314,7 +6314,7 @@
         <v>208</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C38" t="s" s="2">
         <v>209</v>
@@ -6396,7 +6396,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -6448,13 +6448,13 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6505,7 +6505,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6523,7 +6523,7 @@
         <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>79</v>
@@ -6605,7 +6605,7 @@
         <v>135</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>79</v>
@@ -6614,7 +6614,7 @@
         <v>136</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6777,7 +6777,7 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>173</v>
@@ -6863,7 +6863,7 @@
         <v>215</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C43" t="s" s="2">
         <v>216</v>
@@ -6945,7 +6945,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6997,13 +6997,13 @@
         <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7054,7 +7054,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -7072,7 +7072,7 @@
         <v>79</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>79</v>
@@ -7154,7 +7154,7 @@
         <v>135</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>79</v>
@@ -7163,7 +7163,7 @@
         <v>136</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -7274,7 +7274,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -7326,13 +7326,13 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7383,7 +7383,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -7401,7 +7401,7 @@
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>79</v>
@@ -7483,7 +7483,7 @@
         <v>135</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>79</v>
@@ -7492,7 +7492,7 @@
         <v>136</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7821,7 +7821,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7873,13 +7873,13 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7930,7 +7930,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7948,7 +7948,7 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
@@ -8030,7 +8030,7 @@
         <v>135</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>79</v>
@@ -8039,7 +8039,7 @@
         <v>136</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -8368,7 +8368,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8420,13 +8420,13 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8477,7 +8477,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8495,7 +8495,7 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>79</v>
@@ -8577,7 +8577,7 @@
         <v>135</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>79</v>
@@ -8586,7 +8586,7 @@
         <v>136</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8915,7 +8915,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8967,13 +8967,13 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9024,7 +9024,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -9042,7 +9042,7 @@
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>79</v>
@@ -9124,7 +9124,7 @@
         <v>135</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>79</v>
@@ -9133,7 +9133,7 @@
         <v>136</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -9464,7 +9464,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9516,13 +9516,13 @@
         <v>79</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9573,7 +9573,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9591,7 +9591,7 @@
         <v>79</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>79</v>
@@ -9673,7 +9673,7 @@
         <v>135</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>79</v>
@@ -9682,7 +9682,7 @@
         <v>136</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -10013,7 +10013,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -10065,13 +10065,13 @@
         <v>79</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10122,7 +10122,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -10140,7 +10140,7 @@
         <v>79</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>79</v>
@@ -10222,7 +10222,7 @@
         <v>135</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>79</v>
@@ -10231,7 +10231,7 @@
         <v>136</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -10562,7 +10562,7 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>77</v>
@@ -10614,13 +10614,13 @@
         <v>79</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10671,7 +10671,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>77</v>
@@ -10689,7 +10689,7 @@
         <v>79</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>79</v>
@@ -10771,7 +10771,7 @@
         <v>135</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>79</v>
@@ -10780,7 +10780,7 @@
         <v>136</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>77</v>
@@ -11109,7 +11109,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>77</v>
@@ -11161,13 +11161,13 @@
         <v>79</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11218,7 +11218,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>77</v>
@@ -11236,7 +11236,7 @@
         <v>79</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>79</v>
@@ -11318,7 +11318,7 @@
         <v>135</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>79</v>
@@ -11327,7 +11327,7 @@
         <v>136</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>77</v>
@@ -11658,7 +11658,7 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>77</v>
@@ -11710,13 +11710,13 @@
         <v>79</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11767,7 +11767,7 @@
         <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>77</v>
@@ -11785,7 +11785,7 @@
         <v>79</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>79</v>
@@ -11867,7 +11867,7 @@
         <v>135</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>79</v>
@@ -11876,7 +11876,7 @@
         <v>136</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>77</v>
@@ -12207,7 +12207,7 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>77</v>
@@ -12259,13 +12259,13 @@
         <v>79</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12316,7 +12316,7 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>77</v>
@@ -12334,7 +12334,7 @@
         <v>79</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>79</v>
@@ -12416,7 +12416,7 @@
         <v>135</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>79</v>
@@ -12425,7 +12425,7 @@
         <v>136</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>77</v>
@@ -12754,7 +12754,7 @@
         <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>77</v>
@@ -12806,13 +12806,13 @@
         <v>79</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -12863,7 +12863,7 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>77</v>
@@ -12881,7 +12881,7 @@
         <v>79</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>79</v>
@@ -12963,7 +12963,7 @@
         <v>135</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>79</v>
@@ -12972,7 +12972,7 @@
         <v>136</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>77</v>
@@ -13135,7 +13135,7 @@
         <v>79</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L100" t="s" s="2">
         <v>173</v>
@@ -13303,7 +13303,7 @@
         <v>79</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>77</v>
@@ -13355,13 +13355,13 @@
         <v>79</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -13412,7 +13412,7 @@
         <v>79</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>77</v>
@@ -13430,7 +13430,7 @@
         <v>79</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>79</v>
@@ -13512,7 +13512,7 @@
         <v>135</v>
       </c>
       <c r="AC103" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD103" t="s" s="2">
         <v>79</v>
@@ -13521,7 +13521,7 @@
         <v>136</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>77</v>
@@ -13632,7 +13632,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>77</v>
@@ -13684,13 +13684,13 @@
         <v>79</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -13741,7 +13741,7 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>77</v>
@@ -13759,7 +13759,7 @@
         <v>79</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>79</v>
@@ -13841,7 +13841,7 @@
         <v>135</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>79</v>
@@ -13850,7 +13850,7 @@
         <v>136</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>77</v>
@@ -14179,7 +14179,7 @@
         <v>79</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>77</v>
@@ -14231,13 +14231,13 @@
         <v>79</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -14288,7 +14288,7 @@
         <v>79</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>77</v>
@@ -14306,7 +14306,7 @@
         <v>79</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>79</v>
@@ -14388,7 +14388,7 @@
         <v>135</v>
       </c>
       <c r="AC111" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD111" t="s" s="2">
         <v>79</v>
@@ -14397,7 +14397,7 @@
         <v>136</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>77</v>
@@ -14726,7 +14726,7 @@
         <v>79</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>77</v>
@@ -14778,13 +14778,13 @@
         <v>79</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -14835,7 +14835,7 @@
         <v>79</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>77</v>
@@ -14853,7 +14853,7 @@
         <v>79</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>79</v>
@@ -14935,7 +14935,7 @@
         <v>135</v>
       </c>
       <c r="AC116" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD116" t="s" s="2">
         <v>79</v>
@@ -14944,7 +14944,7 @@
         <v>136</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>77</v>
@@ -15275,7 +15275,7 @@
         <v>79</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>77</v>
@@ -15327,13 +15327,13 @@
         <v>79</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -15384,7 +15384,7 @@
         <v>79</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>77</v>
@@ -15402,7 +15402,7 @@
         <v>79</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>79</v>
@@ -15484,7 +15484,7 @@
         <v>135</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>79</v>
@@ -15493,7 +15493,7 @@
         <v>136</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>77</v>
@@ -15656,7 +15656,7 @@
         <v>79</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L123" t="s" s="2">
         <v>173</v>
@@ -15824,7 +15824,7 @@
         <v>79</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>77</v>
@@ -15876,13 +15876,13 @@
         <v>79</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -15933,7 +15933,7 @@
         <v>79</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>77</v>
@@ -15951,7 +15951,7 @@
         <v>79</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>79</v>
@@ -16033,7 +16033,7 @@
         <v>135</v>
       </c>
       <c r="AC126" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD126" t="s" s="2">
         <v>79</v>
@@ -16042,7 +16042,7 @@
         <v>136</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>77</v>
@@ -16373,7 +16373,7 @@
         <v>79</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>77</v>
@@ -16425,13 +16425,13 @@
         <v>79</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -16482,7 +16482,7 @@
         <v>79</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>77</v>
@@ -16500,7 +16500,7 @@
         <v>79</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>79</v>
@@ -16582,7 +16582,7 @@
         <v>135</v>
       </c>
       <c r="AC131" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD131" t="s" s="2">
         <v>79</v>
@@ -16591,7 +16591,7 @@
         <v>136</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>77</v>
@@ -16922,7 +16922,7 @@
         <v>79</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>77</v>
@@ -16974,13 +16974,13 @@
         <v>79</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -17031,7 +17031,7 @@
         <v>79</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>77</v>
@@ -17049,7 +17049,7 @@
         <v>79</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>79</v>
@@ -17131,7 +17131,7 @@
         <v>135</v>
       </c>
       <c r="AC136" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD136" t="s" s="2">
         <v>79</v>
@@ -17140,7 +17140,7 @@
         <v>136</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>77</v>
@@ -17469,7 +17469,7 @@
         <v>79</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>77</v>
@@ -17521,13 +17521,13 @@
         <v>79</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -17578,7 +17578,7 @@
         <v>79</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>77</v>
@@ -17596,7 +17596,7 @@
         <v>79</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM140" t="s" s="2">
         <v>79</v>
@@ -17678,7 +17678,7 @@
         <v>135</v>
       </c>
       <c r="AC141" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD141" t="s" s="2">
         <v>79</v>
@@ -17687,7 +17687,7 @@
         <v>136</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>77</v>
@@ -18018,7 +18018,7 @@
         <v>79</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>77</v>
@@ -18070,13 +18070,13 @@
         <v>79</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -18127,7 +18127,7 @@
         <v>79</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>77</v>
@@ -18145,7 +18145,7 @@
         <v>79</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM145" t="s" s="2">
         <v>79</v>
@@ -18229,7 +18229,7 @@
         <v>135</v>
       </c>
       <c r="AC146" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD146" t="s" s="2">
         <v>79</v>
@@ -18238,7 +18238,7 @@
         <v>136</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>77</v>
@@ -18256,7 +18256,7 @@
         <v>79</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM146" t="s" s="2">
         <v>79</v>
@@ -18349,7 +18349,7 @@
         <v>79</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>77</v>
@@ -18401,13 +18401,13 @@
         <v>79</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -18458,7 +18458,7 @@
         <v>79</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>77</v>
@@ -18476,7 +18476,7 @@
         <v>79</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>79</v>
@@ -18558,7 +18558,7 @@
         <v>135</v>
       </c>
       <c r="AC149" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD149" t="s" s="2">
         <v>79</v>
@@ -18567,7 +18567,7 @@
         <v>136</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>77</v>
@@ -18896,7 +18896,7 @@
         <v>79</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>77</v>
@@ -18948,13 +18948,13 @@
         <v>79</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -19005,7 +19005,7 @@
         <v>79</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>77</v>
@@ -19023,7 +19023,7 @@
         <v>79</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM153" t="s" s="2">
         <v>79</v>
@@ -19107,7 +19107,7 @@
         <v>135</v>
       </c>
       <c r="AC154" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD154" t="s" s="2">
         <v>79</v>
@@ -19116,7 +19116,7 @@
         <v>136</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>77</v>
@@ -19134,7 +19134,7 @@
         <v>79</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM154" t="s" s="2">
         <v>79</v>
@@ -19227,7 +19227,7 @@
         <v>79</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>77</v>
@@ -19279,13 +19279,13 @@
         <v>79</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -19336,7 +19336,7 @@
         <v>79</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>77</v>
@@ -19354,7 +19354,7 @@
         <v>79</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>79</v>
@@ -19436,7 +19436,7 @@
         <v>135</v>
       </c>
       <c r="AC157" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD157" t="s" s="2">
         <v>79</v>
@@ -19445,7 +19445,7 @@
         <v>136</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>77</v>
@@ -19776,7 +19776,7 @@
         <v>79</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>77</v>
@@ -19828,13 +19828,13 @@
         <v>79</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -19885,7 +19885,7 @@
         <v>79</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>77</v>
@@ -19903,7 +19903,7 @@
         <v>79</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>79</v>
@@ -19985,7 +19985,7 @@
         <v>135</v>
       </c>
       <c r="AC162" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD162" t="s" s="2">
         <v>79</v>
@@ -19994,7 +19994,7 @@
         <v>136</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>77</v>
@@ -20325,7 +20325,7 @@
         <v>79</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>77</v>
@@ -20377,13 +20377,13 @@
         <v>79</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -20434,7 +20434,7 @@
         <v>79</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>77</v>
@@ -20452,7 +20452,7 @@
         <v>79</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM166" t="s" s="2">
         <v>79</v>
@@ -20534,7 +20534,7 @@
         <v>135</v>
       </c>
       <c r="AC167" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD167" t="s" s="2">
         <v>79</v>
@@ -20543,7 +20543,7 @@
         <v>136</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>77</v>
@@ -22133,13 +22133,13 @@
         <v>79</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
@@ -22190,7 +22190,7 @@
         <v>79</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>77</v>
@@ -22208,7 +22208,7 @@
         <v>79</v>
       </c>
       <c r="AL182" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM182" t="s" s="2">
         <v>79</v>
@@ -22292,7 +22292,7 @@
         <v>135</v>
       </c>
       <c r="AC183" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD183" t="s" s="2">
         <v>79</v>
@@ -22301,7 +22301,7 @@
         <v>136</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>77</v>
@@ -22319,7 +22319,7 @@
         <v>79</v>
       </c>
       <c r="AL183" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM183" t="s" s="2">
         <v>79</v>
@@ -22690,7 +22690,7 @@
         <v>88</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L187" t="s" s="2">
         <v>485</v>
@@ -23132,13 +23132,13 @@
         <v>79</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N191" s="2"/>
       <c r="O191" s="2"/>
@@ -23189,7 +23189,7 @@
         <v>79</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>77</v>
@@ -23207,7 +23207,7 @@
         <v>79</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM191" t="s" s="2">
         <v>79</v>
@@ -23291,7 +23291,7 @@
         <v>135</v>
       </c>
       <c r="AC192" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD192" t="s" s="2">
         <v>79</v>
@@ -23300,7 +23300,7 @@
         <v>136</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>77</v>
@@ -23318,7 +23318,7 @@
         <v>79</v>
       </c>
       <c r="AL192" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM192" t="s" s="2">
         <v>79</v>
@@ -23689,7 +23689,7 @@
         <v>88</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L196" t="s" s="2">
         <v>485</v>
@@ -24131,13 +24131,13 @@
         <v>79</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N200" s="2"/>
       <c r="O200" s="2"/>
@@ -24188,7 +24188,7 @@
         <v>79</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>77</v>
@@ -24206,7 +24206,7 @@
         <v>79</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM200" t="s" s="2">
         <v>79</v>
@@ -24290,7 +24290,7 @@
         <v>135</v>
       </c>
       <c r="AC201" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD201" t="s" s="2">
         <v>79</v>
@@ -24299,7 +24299,7 @@
         <v>136</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>77</v>
@@ -24317,7 +24317,7 @@
         <v>79</v>
       </c>
       <c r="AL201" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM201" t="s" s="2">
         <v>79</v>
@@ -24688,7 +24688,7 @@
         <v>88</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L205" t="s" s="2">
         <v>485</v>
@@ -25130,13 +25130,13 @@
         <v>79</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" s="2"/>
@@ -25187,7 +25187,7 @@
         <v>79</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>77</v>
@@ -25205,7 +25205,7 @@
         <v>79</v>
       </c>
       <c r="AL209" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM209" t="s" s="2">
         <v>79</v>
@@ -25289,7 +25289,7 @@
         <v>135</v>
       </c>
       <c r="AC210" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD210" t="s" s="2">
         <v>79</v>
@@ -25298,7 +25298,7 @@
         <v>136</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>77</v>
@@ -25316,7 +25316,7 @@
         <v>79</v>
       </c>
       <c r="AL210" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM210" t="s" s="2">
         <v>79</v>
@@ -25687,7 +25687,7 @@
         <v>88</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L214" t="s" s="2">
         <v>485</v>
@@ -26129,13 +26129,13 @@
         <v>79</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N218" s="2"/>
       <c r="O218" s="2"/>
@@ -26186,7 +26186,7 @@
         <v>79</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>77</v>
@@ -26204,7 +26204,7 @@
         <v>79</v>
       </c>
       <c r="AL218" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM218" t="s" s="2">
         <v>79</v>
@@ -26288,7 +26288,7 @@
         <v>135</v>
       </c>
       <c r="AC219" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD219" t="s" s="2">
         <v>79</v>
@@ -26297,7 +26297,7 @@
         <v>136</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>77</v>
@@ -26315,7 +26315,7 @@
         <v>79</v>
       </c>
       <c r="AL219" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM219" t="s" s="2">
         <v>79</v>
@@ -26686,7 +26686,7 @@
         <v>88</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L223" t="s" s="2">
         <v>485</v>
@@ -27128,13 +27128,13 @@
         <v>79</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N227" s="2"/>
       <c r="O227" s="2"/>
@@ -27185,7 +27185,7 @@
         <v>79</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>77</v>
@@ -27203,7 +27203,7 @@
         <v>79</v>
       </c>
       <c r="AL227" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM227" t="s" s="2">
         <v>79</v>
@@ -27287,7 +27287,7 @@
         <v>135</v>
       </c>
       <c r="AC228" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AD228" t="s" s="2">
         <v>79</v>
@@ -27296,7 +27296,7 @@
         <v>136</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>77</v>
@@ -27314,7 +27314,7 @@
         <v>79</v>
       </c>
       <c r="AL228" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM228" t="s" s="2">
         <v>79</v>
@@ -27685,7 +27685,7 @@
         <v>88</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L232" t="s" s="2">
         <v>485</v>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T10:03:25+00:00</t>
+    <t>2026-06-25T10:20:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T10:20:08+00:00</t>
+    <t>2026-06-25T14:41:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -468,7 +468,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}motivationLocaleRequired:La motivation locale doit être renseignée si la motivation de la décision est '9999' (Autre). {(extension.where(url='motivation').valueCodeableConcept.coding.where(code='9999').exists()) implies (extension.where(url='motivationLocale').valueString.exists())}DateEffetClotureCardinality:Si typeDecision = '5' (Clôture de droit) alors dateEffetCloture est obligatoire. {(extension.where(url='typeDecision').valueCodeableConcept.coding.code='5'.exists()) implies (extension.where(url='dateEffetCloture').exists())}</t>
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}motivationLocaleRequired:La motivation locale doit être renseignée si la motivation de la décision est '9999' (Autre). {(extension.where(url='motivation').valueCodeableConcept.coding.where(code='9999').exists()) implies (extension.where(url='motivationLocale').valueString.exists())}DateEffetClotureCardinality:Si typeDecision = '5' (Clôture de droit) alors dateEffetCloture est obligatoire. {(extension.where(url='typeDecision').valueCodeableConcept.coding.where(code='5').exists()) implies (extension.where(url='dateEffetCloture').exists())}</t>
   </si>
   <si>
     <t>Basic.extension:TDDUIDecision.id</t>
@@ -688,8 +688,8 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}FormationCardinality:Formation est obligatoire si typeDroitPrestation = '11.1' (Orientation en Centre de rééducation professionnelle (CRP)). {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='11.1') implies (extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='formation').exists())}PrecisionOrientationValues7.8:Si typeDroitPrestation = '7.8' (Orientation vers un Service d'éducation spéciale et de soins à domicile (SESSAD)) alors precisionOrientation entre '1' et
- '6' {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='7.8') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=1) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=6))}PrecisionOrientationValues7.9:Si typeDroitPrestation = '7.9' (Orientation vers un Service d'accompagnement familial et d'éducation précoce (SAFEP)) alors precisionOrientation entre '7' et '8' {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='7.9') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=7) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=8))}PrecisionOrientationValues13.1-13.2:Si typeDroitPrestation = '13.1' (Orientation vers un établissement d'accueil non médicalisé) ou '13.2' (Orientation vers un établissement d'accueil médicalisé en tout ou partie) alors precisionOrientation est interdit {((extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='13.1') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='13.2')) implies (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').exists().not())}PrecisionOrientationValues8.3:Si typeDroitPrestation = '8.3' (Orientation en Enseignement adapté (SEGPA/EREA)) alors precisionOrientation entre '9' et '10'  {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.3') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=9) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=10))}PrecisionOrientationValues8.6:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) alors precisionOrientation = 'UEA' (Unité d'enseignement élémentaire autisme) ou 'UEM' (Unité d'enseignement en maternelle plan autisme). {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.6') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code='UEA') or (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code='UEM'))}temporaliteAccueilCardinalityViaCategorieDroitPrestation:Si categorieDroitPrestation = '13' (Orientation ESMS Adultes) ou '7' (Orientation ESMS Enfants) alors temporaliteAccueil est obligatoire. {((extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='13') or (extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='7')) implies (extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil').exists())}temporaliteAccueilCardinalityViaTypeDroitPrestation:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) ou '8.7' (Orientation vers une Scolarisation en milieu ordinaire à temps partagé) ou '8.8' (Orientation vers une Unité d'enseignement et une scolarisation en ULIS à temps partagé) ou '8.10' (Orientation vers une unité d'enseignement et une scolarisation en enseignement adapté à temps partagé) alors la temporalité d'accueil est obligatoire. {((extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.6') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.7') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.8') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.10')) implies (extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil').exists())}cretonCardinality:Si categorieDroitPrestation = '7' (ESSMS enfant) alors Creton est obligatoire {((extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='7') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code.matches('^7[.][0-9]+$'))) implies (extension.where(url='creton').exists())}</t>
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}FormationCardinality:Formation est obligatoire si typeDroitPrestation = '11.1' (Orientation en Centre de rééducation professionnelle (CRP)). {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='11.1') implies (extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='formation'))}PrecisionOrientationValues7.8:Si typeDroitPrestation = '7.8' (Orientation vers un Service d'éducation spéciale et de soins à domicile (SESSAD)) alors precisionOrientation entre '1' et
+ '6' {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='7.8') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=1) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=6))}PrecisionOrientationValues7.9:Si typeDroitPrestation = '7.9' (Orientation vers un Service d'accompagnement familial et d'éducation précoce (SAFEP)) alors precisionOrientation entre '7' et '8' {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='7.9') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=7) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=8))}PrecisionOrientationValues13.1-13.2:Si typeDroitPrestation = '13.1' (Orientation vers un établissement d'accueil non médicalisé) ou '13.2' (Orientation vers un établissement d'accueil médicalisé en tout ou partie) alors precisionOrientation est interdit {((extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='13.1') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='13.2')) implies (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').not())}PrecisionOrientationValues8.3:Si typeDroitPrestation = '8.3' (Orientation en Enseignement adapté (SEGPA/EREA)) alors precisionOrientation entre '9' et '10'  {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.3') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=9) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=10))}PrecisionOrientationValues8.6:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) alors precisionOrientation = 'UEA' (Unité d'enseignement élémentaire autisme) ou 'UEM' (Unité d'enseignement en maternelle plan autisme). {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.6') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code='UEA') or (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code='UEM'))}temporaliteAccueilCardinalityViaCategorieDroitPrestation:Si categorieDroitPrestation = '13' (Orientation ESMS Adultes) ou '7' (Orientation ESMS Enfants) alors temporaliteAccueil est obligatoire. {((extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='13') or (extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='7')) implies (extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil'))}temporaliteAccueilCardinalityViaTypeDroitPrestation:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) ou '8.7' (Orientation vers une Scolarisation en milieu ordinaire à temps partagé) ou '8.8' (Orientation vers une Unité d'enseignement et une scolarisation en ULIS à temps partagé) ou '8.10' (Orientation vers une unité d'enseignement et une scolarisation en enseignement adapté à temps partagé) alors la temporalité d'accueil est obligatoire. {((extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.6') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.7') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.8') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.10')) implies (extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil'))}cretonCardinality:Si categorieDroitPrestation = '7' (ESSMS enfant) alors Creton est obligatoire {((extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='7') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code.matches('^7[.][0-9]+$'))) implies (extension.where(url='creton'))}</t>
   </si>
   <si>
     <t>DroitPrestation</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0-ballot</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T14:41:02+00:00</t>
+    <t>2026-06-30T07:08:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
